--- a/backend/dashboard/Dashboard.xlsx
+++ b/backend/dashboard/Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Engineering\New folder\Company_details\dashboard\backend\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5495895-C9C3-4E2B-AAFA-19F2A76F8BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0BC294-1CDD-4946-8E5B-4780B7F28D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$D$1:$D$1003</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$E$1:$E$1003</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,12 +34,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="563">
   <si>
     <t>Next Followup</t>
   </si>
   <si>
     <t>Last Follow up date</t>
+  </si>
+  <si>
+    <t>No of follow ups</t>
   </si>
   <si>
     <t>Initiated</t>
@@ -1555,9 +1558,6 @@
     <t>Mohammad Rafiuddin &lt;mohammad.rafiuddin@ceew.in&gt;</t>
   </si>
   <si>
-    <t>Wednesday and Thursday between 3 and 5 PM for a call.</t>
-  </si>
-  <si>
     <t>11 Feb 2026 Requirement Discussed</t>
   </si>
   <si>
@@ -1963,7 +1963,7 @@
     <t>chirag@teleysia.com</t>
   </si>
   <si>
-    <t>meeting on March 6th at 4:00 PM</t>
+    <t>Requested meeting on March 6th at 4:00 PM</t>
   </si>
   <si>
     <t>Samit</t>
@@ -2095,6 +2095,9 @@
   </si>
   <si>
     <t xml:space="preserve">sent number </t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/05/2026 4pm </t>
   </si>
 </sst>
 </file>
@@ -2457,10 +2460,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2701,8 +2707,11 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2922,23 +2931,25 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AK89"/>
+  <dimension ref="A1:AL89"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="14.453125" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="18.6328125" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" customWidth="1"/>
-    <col min="7" max="7" width="32.90625" customWidth="1"/>
-    <col min="8" max="8" width="25.36328125" customWidth="1"/>
-    <col min="9" max="9" width="30.26953125" customWidth="1"/>
-    <col min="10" max="10" width="21" customWidth="1"/>
-    <col min="11" max="13" width="21.453125" customWidth="1"/>
-    <col min="14" max="16" width="28.6328125" customWidth="1"/>
-    <col min="17" max="17" width="21.453125" customWidth="1"/>
+    <col min="1" max="4" width="14.453125" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="18.6328125" customWidth="1"/>
+    <col min="7" max="7" width="19.453125" customWidth="1"/>
+    <col min="8" max="8" width="32.90625" customWidth="1"/>
+    <col min="9" max="9" width="25.36328125" customWidth="1"/>
+    <col min="10" max="10" width="30.26953125" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="12" max="13" width="21.453125" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="33.08984375" customWidth="1"/>
+    <col min="16" max="17" width="28.6328125" customWidth="1"/>
+    <col min="18" max="18" width="21.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="26">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2948,78 +2959,79 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="3"/>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3"/>
-      <c r="AE1" s="3"/>
-      <c r="AF1" s="3"/>
-      <c r="AG1" s="3"/>
-      <c r="AH1" s="3"/>
-      <c r="AI1" s="3"/>
-      <c r="AJ1" s="3"/>
-      <c r="AK1" s="3"/>
-    </row>
-    <row r="2" spans="1:37" ht="15.75" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4"/>
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4"/>
+    </row>
+    <row r="2" spans="1:38" ht="15.75" customHeight="1">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -3031,4089 +3043,4168 @@
       <c r="G2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4" t="s">
+      <c r="K2" s="5"/>
+      <c r="L2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="8" t="s">
+      <c r="M2" s="5"/>
+      <c r="N2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37" ht="15.75" customHeight="1">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="Q2" s="8"/>
+      <c r="R2" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="S2" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" ht="15.75" customHeight="1">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="I3" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="J3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="5" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="7" t="s">
+      <c r="H4" s="13" t="s">
         <v>39</v>
       </c>
+      <c r="I4" s="5"/>
       <c r="J4" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4" t="s">
+      <c r="K4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="R4" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37" ht="15.75" customHeight="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="13" t="s">
+      <c r="L4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="S4" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" ht="15.75" customHeight="1">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="5" t="s">
         <v>44</v>
       </c>
       <c r="G5" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="7" t="s">
+      <c r="H5" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4" t="s">
+      <c r="I5" s="5"/>
+      <c r="J5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="R5" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37" ht="15.75" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="L5" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="M5" s="5"/>
+      <c r="N5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" ht="15.75" customHeight="1">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4" t="s">
+      <c r="J6" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="R6" s="4" t="s">
+      <c r="K6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="7" spans="1:37">
-      <c r="A7" s="4"/>
-      <c r="B7" s="16">
+      <c r="S6" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38">
+      <c r="A7" s="5"/>
+      <c r="B7" s="17">
         <v>46071</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="C7" s="17"/>
+      <c r="D7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="7" t="s">
+      <c r="H7" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4" t="s">
+      <c r="I7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="R7" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37">
-      <c r="A8" s="4"/>
-      <c r="B8" s="16">
+      <c r="M7" s="5"/>
+      <c r="N7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="S7" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38">
+      <c r="A8" s="5"/>
+      <c r="B8" s="17">
         <v>46071</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="C8" s="17"/>
+      <c r="D8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="17" t="s">
+      <c r="I8" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="8" t="s">
+      <c r="J8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="R8" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37" ht="15.75" customHeight="1">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="18" t="s">
+      <c r="M8" s="5"/>
+      <c r="N8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="S8" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" ht="15.75" customHeight="1">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>69</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="H9" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="K9" s="20" t="s">
+      <c r="H9" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="O9" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="21" t="s">
+      <c r="I9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="R9" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="S9" s="22"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22"/>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="22"/>
-      <c r="AC9" s="22"/>
-      <c r="AD9" s="22"/>
-      <c r="AE9" s="22"/>
-      <c r="AF9" s="22"/>
-      <c r="AG9" s="22"/>
-      <c r="AH9" s="22"/>
-      <c r="AI9" s="22"/>
-      <c r="AJ9" s="22"/>
-      <c r="AK9" s="22"/>
-    </row>
-    <row r="10" spans="1:37">
-      <c r="A10" s="23">
+      <c r="M9" s="19"/>
+      <c r="N9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="S9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="23"/>
+      <c r="W9" s="23"/>
+      <c r="X9" s="23"/>
+      <c r="Y9" s="23"/>
+      <c r="Z9" s="23"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="23"/>
+      <c r="AC9" s="23"/>
+      <c r="AD9" s="23"/>
+      <c r="AE9" s="23"/>
+      <c r="AF9" s="23"/>
+      <c r="AG9" s="23"/>
+      <c r="AH9" s="23"/>
+      <c r="AI9" s="23"/>
+      <c r="AJ9" s="23"/>
+      <c r="AK9" s="23"/>
+      <c r="AL9" s="23"/>
+    </row>
+    <row r="10" spans="1:38">
+      <c r="A10" s="24">
         <v>46085</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="24">
         <v>46078</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="C10" s="24"/>
+      <c r="D10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="4" t="s">
+      <c r="H10" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="J10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" s="4" t="s">
+      <c r="I10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="L10" s="25">
+      <c r="K10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="M10" s="26">
         <v>46071</v>
       </c>
-      <c r="M10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4" t="s">
+      <c r="N10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="R10" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37" ht="15.75" customHeight="1">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4" t="s">
+      <c r="P10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="S10" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" ht="15.75" customHeight="1">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="14" t="s">
+      <c r="E11" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="5"/>
+      <c r="G11" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4" t="s">
+      <c r="J11" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="N11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4" t="s">
+      <c r="K11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="R11" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37">
-      <c r="A12" s="16">
+      <c r="O11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38">
+      <c r="A12" s="17">
         <v>46085</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="17">
         <v>46077</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="C12" s="17"/>
+      <c r="D12" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="5" t="s">
         <v>95</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="J12" s="26" t="s">
+      <c r="J12" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4" t="s">
+      <c r="K12" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="S12" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" ht="15.75" customHeight="1">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="8" t="s">
+      <c r="H13" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K13" s="26" t="s">
+      <c r="I13" s="5"/>
+      <c r="J13" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4" t="s">
+      <c r="K13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="R13" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37">
-      <c r="A14" s="16">
+      <c r="M13" s="5"/>
+      <c r="N13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="S13" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38">
+      <c r="A14" s="17">
         <v>46085</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="17">
         <v>46077</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="C14" s="17"/>
+      <c r="D14" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="H14" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K14" s="8" t="s">
+      <c r="I14" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N14" s="7" t="s">
+      <c r="J14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L14" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="O14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4" t="s">
+      <c r="M14" s="5"/>
+      <c r="N14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="R14" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37">
-      <c r="A15" s="16">
+      <c r="P14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38">
+      <c r="A15" s="17">
         <v>46085</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="17">
         <v>46077</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="C15" s="17"/>
+      <c r="D15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="I15" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S15" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H15" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R15" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" s="4"/>
-      <c r="L16" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="O16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="R16" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="16">
+      <c r="S16" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" s="17">
         <v>46085</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="17">
         <v>46077</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E17" s="4" t="s">
+      <c r="C17" s="17"/>
+      <c r="D17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" s="4" t="s">
+      <c r="H17" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="I17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="7" t="s">
+      <c r="L17" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="R17" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4" t="s">
+      <c r="M17" s="5"/>
+      <c r="N17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="S17" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="H18" s="27"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4" t="s">
+      <c r="H18" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4" t="s">
+      <c r="I18" s="28"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="O18" s="27" t="s">
+      <c r="N18" s="5"/>
+      <c r="O18" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="P18" s="4" t="s">
+      <c r="P18" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="Q18" s="4" t="s">
+      <c r="Q18" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="R18" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="R18" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="S18" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" s="4" t="s">
+      <c r="I19" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="K19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4" t="s">
+      <c r="J19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="R19" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="16">
+      <c r="L19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="S19" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" s="17">
         <v>46087</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="17">
         <v>46077</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E20" s="4" t="s">
+      <c r="C20" s="17"/>
+      <c r="D20" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="G20" s="28" t="s">
+      <c r="G20" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="8" t="s">
+      <c r="H20" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="J20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" s="7" t="s">
+      <c r="I20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R20" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="K20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="M20" s="5"/>
+      <c r="N20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S20" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="K21" s="4" t="s">
+      <c r="H21" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R21" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="50.5">
-      <c r="A22" s="29" t="s">
+      <c r="I21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="L21" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B22" s="30">
+      <c r="M21" s="5"/>
+      <c r="N21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S21" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="50.5">
+      <c r="A22" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="B22" s="31">
         <v>46077</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="C22" s="31"/>
+      <c r="D22" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="31" t="s">
+      <c r="F22" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J22" s="4" t="s">
+      <c r="H22" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="K22" s="4"/>
-      <c r="L22" s="12" t="s">
+      <c r="I22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O22" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4" t="s">
+      <c r="L22" s="5"/>
+      <c r="M22" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="R22" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="37.5">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="N22" s="5"/>
+      <c r="O22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="S22" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="37.5">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="H23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I23" s="4" t="s">
+      <c r="H23" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="4" t="s">
+      <c r="I23" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="M23" s="4"/>
-      <c r="N23" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="O23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P23" s="4" t="s">
+      <c r="K23" s="5"/>
+      <c r="L23" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="Q23" s="4" t="s">
+      <c r="N23" s="5"/>
+      <c r="O23" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q23" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="R23" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="37.5">
-      <c r="A24" s="32">
+      <c r="R23" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="S23" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="37.5">
+      <c r="A24" s="33">
         <v>46086</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="33">
         <v>46078</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E24" s="4" t="s">
+      <c r="C24" s="33"/>
+      <c r="D24" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I24" s="7" t="s">
+      <c r="H24" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="J24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K24" s="8" t="s">
+      <c r="I24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="33" t="s">
+      <c r="K24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L24" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="R24" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="38">
-      <c r="A25" s="16">
+      <c r="M24" s="5"/>
+      <c r="N24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="S24" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="51">
+      <c r="A25" s="17">
         <v>46085</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="17">
         <v>46077</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E25" s="4" t="s">
+      <c r="C25" s="17"/>
+      <c r="D25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" s="8" t="s">
+      <c r="H25" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7" t="s">
+      <c r="I25" s="5"/>
+      <c r="J25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L25" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="N25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R25" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="63">
-      <c r="A26" s="16">
+      <c r="M25" s="8"/>
+      <c r="N25" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S25" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="63">
+      <c r="A26" s="17">
         <v>46085</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="17">
         <v>46077</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="E26" s="4" t="s">
+      <c r="C26" s="17"/>
+      <c r="D26" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="G26" s="24" t="s">
+      <c r="G26" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="7" t="s">
+      <c r="H26" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="M26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R26" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="116">
-      <c r="A27" s="16">
+      <c r="I26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S26" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="116">
+      <c r="A27" s="17">
         <v>46085</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="17">
         <v>46077</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="E27" s="4" t="s">
+      <c r="C27" s="17"/>
+      <c r="D27" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="H27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="34" t="s">
+      <c r="H27" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="M27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N27" s="34" t="s">
+      <c r="I27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M27" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="O27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="4" t="s">
+      <c r="N27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O27" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="R27" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="63">
-      <c r="A28" s="16">
+      <c r="P27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="S27" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="63">
+      <c r="B28" s="17">
         <v>46085</v>
       </c>
-      <c r="B28" s="16">
+      <c r="C28" s="17"/>
+      <c r="D28" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="S28" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="25.5">
+      <c r="A29" s="17">
+        <v>46085</v>
+      </c>
+      <c r="B29" s="17">
         <v>46077</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="N28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="R28" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="25.5">
-      <c r="A29" s="16">
+      <c r="C29" s="17"/>
+      <c r="D29" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P29" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S29" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="42">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M30" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="N30" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="S30" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="125.5">
+      <c r="A31" s="17">
         <v>46085</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B31" s="17">
         <v>46077</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R29" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="42">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="C31" s="17"/>
+      <c r="D31" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="N30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="R30" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="138">
-      <c r="A31" s="16">
-        <v>46085</v>
-      </c>
-      <c r="B31" s="16">
-        <v>46077</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="5" t="s">
         <v>225</v>
       </c>
       <c r="G31" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="H31" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I31" s="7" t="s">
+      <c r="H31" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="J31" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K31" s="8" t="s">
+      <c r="I31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" s="7" t="s">
+      <c r="K31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L31" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="O31" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4" t="s">
+      <c r="M31" s="5"/>
+      <c r="N31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O31" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="R31" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="50">
-      <c r="A32" s="16">
+      <c r="P31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="S31" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="50">
+      <c r="A32" s="17">
         <v>46085</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="17">
         <v>46077</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="E32" s="4" t="s">
+      <c r="C32" s="17"/>
+      <c r="D32" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="G32" s="24" t="s">
+      <c r="G32" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K32" s="7" t="s">
+      <c r="I32" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8" t="s">
+      <c r="J32" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L32" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="N32" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O32" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="R32" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="50.5">
-      <c r="A33" s="16">
+      <c r="M32" s="9"/>
+      <c r="N32" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P32" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="S32" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="50.5">
+      <c r="A33" s="17">
         <v>46085</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="17">
         <v>46077</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="17"/>
+      <c r="D33" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="G33" s="36" t="s">
-        <v>241</v>
-      </c>
-      <c r="H33" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O33" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="R33" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="37.5">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E34" s="4" t="s">
+      <c r="S33" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="37.5">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K34" s="37">
+      <c r="H34" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L34" s="38">
         <v>46030</v>
       </c>
-      <c r="L34" s="37">
+      <c r="M34" s="38">
         <v>46030</v>
       </c>
-      <c r="M34" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N34" s="27"/>
-      <c r="O34" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="R34" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="75.5">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35" s="38" t="s">
-        <v>248</v>
-      </c>
-      <c r="E35" s="4" t="s">
+      <c r="N34" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O34" s="28"/>
+      <c r="P34" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="S34" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="63">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="G35" s="39" t="s">
+      <c r="G35" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="H35" s="40" t="s">
         <v>252</v>
       </c>
-      <c r="I35" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J35" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8" t="s">
+      <c r="I35" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="N35" s="4" t="s">
+      <c r="J35" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K35" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="O35" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R35" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" ht="38">
-      <c r="A36" s="16">
+      <c r="O35" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="P35" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S35" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="38">
+      <c r="A36" s="17">
         <v>46085</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="17">
         <v>46077</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="E36" s="4" t="s">
+      <c r="C36" s="17"/>
+      <c r="D36" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="5" t="s">
         <v>257</v>
       </c>
       <c r="G36" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="H36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K36" s="7" t="s">
+      <c r="H36" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R36" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" ht="63">
-      <c r="A37" s="16">
+      <c r="I36" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P36" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S36" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="100.5">
+      <c r="A37" s="17">
         <v>46085</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="17">
         <v>46077</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="E37" s="4" t="s">
+      <c r="C37" s="17"/>
+      <c r="D37" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="G37" s="91" t="s">
+      <c r="G37" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="H37" s="92"/>
-      <c r="I37" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J37" s="27"/>
-      <c r="K37" s="7" t="s">
+      <c r="H37" s="92" t="s">
         <v>264</v>
       </c>
-      <c r="L37" s="8"/>
-      <c r="M37" s="4" t="s">
+      <c r="I37" s="93"/>
+      <c r="J37" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K37" s="28"/>
+      <c r="L37" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="N37" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O37" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R37" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="50">
-      <c r="A38" s="16">
+      <c r="M37" s="9"/>
+      <c r="N37" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P37" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S37" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="50">
+      <c r="A38" s="17">
         <v>46085</v>
       </c>
-      <c r="B38" s="41" t="s">
-        <v>163</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="E38" s="4" t="s">
+      <c r="B38" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="C38" s="42"/>
+      <c r="D38" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="5" t="s">
         <v>268</v>
       </c>
       <c r="G38" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K38" s="7" t="s">
+      <c r="H38" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N38" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O38" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R38" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="50.5">
-      <c r="A39" s="16">
+      <c r="I38" s="5"/>
+      <c r="J38" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P38" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S38" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="50.5">
+      <c r="A39" s="17">
         <v>46085</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="17">
         <v>46077</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="E39" s="4" t="s">
+      <c r="C39" s="17"/>
+      <c r="D39" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="H39" s="7" t="s">
+      <c r="H39" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K39" s="7" t="s">
+      <c r="I39" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N39" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O39" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R39" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="50.5">
-      <c r="A40" s="16">
+      <c r="J39" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P39" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S39" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="50.5">
+      <c r="A40" s="17">
         <v>46085</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="17">
         <v>46077</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="E40" s="4" t="s">
+      <c r="C40" s="17"/>
+      <c r="D40" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G40" s="42" t="s">
+      <c r="G40" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H40" s="43" t="s">
         <v>281</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N40" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O40" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="8" t="s">
+      <c r="I40" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="R40" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" ht="88">
-      <c r="A41" s="16">
+      <c r="J40" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P40" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="S40" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="88">
+      <c r="A41" s="17">
         <v>46085</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="17">
         <v>46077</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="E41" s="4" t="s">
+      <c r="C41" s="17"/>
+      <c r="D41" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="5" t="s">
         <v>285</v>
       </c>
       <c r="G41" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="I41" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J41" s="8" t="s">
+      <c r="I41" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="K41" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N41" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O41" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R41" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="50.5">
-      <c r="A42" s="16">
+      <c r="J41" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P41" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S41" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="50.5">
+      <c r="A42" s="17">
         <v>46085</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="17">
         <v>46077</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="E42" s="4" t="s">
+      <c r="C42" s="17"/>
+      <c r="D42" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="F42" s="43" t="s">
+      <c r="F42" s="5" t="s">
         <v>291</v>
       </c>
       <c r="G42" s="44" t="s">
         <v>292</v>
       </c>
-      <c r="H42" s="24" t="s">
+      <c r="H42" s="45" t="s">
         <v>293</v>
       </c>
-      <c r="I42" s="8" t="s">
+      <c r="I42" s="25" t="s">
         <v>294</v>
       </c>
-      <c r="J42" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N42" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O42" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="7" t="s">
+      <c r="J42" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="R42" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="28">
-      <c r="A43" s="30">
+      <c r="K42" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O42" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P42" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q42" s="5"/>
+      <c r="R42" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="S42" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="28">
+      <c r="A43" s="31">
         <v>46085</v>
       </c>
-      <c r="B43" s="30">
+      <c r="B43" s="31">
         <v>46077</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="E43" s="4" t="s">
+      <c r="C43" s="31"/>
+      <c r="D43" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G43" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="H43" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K43" s="4" t="s">
+      <c r="H43" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" s="8" t="s">
+      <c r="I43" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L43" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="O43" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R43" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="76">
-      <c r="A44" s="16">
+      <c r="M43" s="5"/>
+      <c r="N43" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="P43" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S43" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="76">
+      <c r="A44" s="17">
         <v>46085</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="17">
         <v>46077</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="E44" s="4" t="s">
+      <c r="C44" s="17"/>
+      <c r="D44" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="G44" s="45" t="s">
+      <c r="G44" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="H44" s="24" t="s">
+      <c r="H44" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J44" s="4" t="s">
+      <c r="I44" s="25" t="s">
         <v>307</v>
       </c>
-      <c r="K44" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N44" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O44" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R44" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" ht="50">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D45" s="4" t="s">
+      <c r="J44" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K44" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="L44" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O44" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P44" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S44" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="50">
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="G45" s="7" t="s">
+      <c r="G45" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="H45" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="I45" s="8" t="s">
+      <c r="I45" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="J45" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K45" s="4" t="s">
+      <c r="J45" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O45" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R45" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" ht="125.5">
-      <c r="A46" s="16">
+      <c r="K45" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O45" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P45" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q45" s="5"/>
+      <c r="R45" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S45" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="125.5">
+      <c r="A46" s="17">
         <v>46085</v>
       </c>
-      <c r="B46" s="16">
+      <c r="B46" s="17">
         <v>46077</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="E46" s="4" t="s">
+      <c r="C46" s="17"/>
+      <c r="D46" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E46" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="G46" s="46" t="s">
+      <c r="G46" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="H46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I46" s="7" t="s">
+      <c r="H46" s="47" t="s">
         <v>319</v>
       </c>
-      <c r="J46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R46" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" ht="50">
-      <c r="A47" s="16">
+      <c r="I46" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O46" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P46" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S46" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="50">
+      <c r="A47" s="17">
         <v>46085</v>
       </c>
-      <c r="B47" s="16">
+      <c r="B47" s="17">
         <v>46077</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E47" s="4" t="s">
+      <c r="C47" s="17"/>
+      <c r="D47" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E47" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="F47" s="47" t="s">
+      <c r="F47" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="G47" s="15" t="s">
+      <c r="G47" s="48" t="s">
         <v>323</v>
       </c>
-      <c r="H47" s="7" t="s">
+      <c r="H47" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="I47" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K47" s="7" t="s">
+      <c r="I47" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4" t="s">
+      <c r="J47" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L47" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="N47" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O47" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R47" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="50">
-      <c r="A48" s="16">
+      <c r="M47" s="5"/>
+      <c r="N47" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="O47" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P47" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S47" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="50">
+      <c r="A48" s="17">
         <v>46085</v>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="17">
         <v>46077</v>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="48" t="s">
-        <v>327</v>
-      </c>
-      <c r="E48" s="26" t="s">
+      <c r="C48" s="17"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="49" t="s">
         <v>328</v>
       </c>
-      <c r="F48" s="49" t="s">
+      <c r="F48" s="27" t="s">
         <v>329</v>
       </c>
       <c r="G48" s="50" t="s">
         <v>330</v>
       </c>
-      <c r="I48" s="48" t="s">
-        <v>104</v>
-      </c>
-      <c r="J48" s="48" t="s">
+      <c r="H48" s="51" t="s">
         <v>331</v>
       </c>
-      <c r="K48" s="7"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
-    </row>
-    <row r="49" spans="1:37" ht="50">
-      <c r="A49" s="16">
+      <c r="J48" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="K48" s="49" t="s">
+        <v>332</v>
+      </c>
+      <c r="L48" s="8"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
+      <c r="R48" s="5"/>
+      <c r="S48" s="5"/>
+    </row>
+    <row r="49" spans="1:38" ht="50">
+      <c r="A49" s="17">
         <v>46085</v>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="17">
         <v>46077</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="D49" s="4" t="s">
+      <c r="C49" s="17"/>
+      <c r="D49" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="E49" s="51" t="s">
+      <c r="E49" s="5" t="s">
         <v>334</v>
       </c>
       <c r="F49" s="52" t="s">
         <v>335</v>
       </c>
-      <c r="G49" s="48" t="s">
+      <c r="G49" s="53" t="s">
         <v>336</v>
       </c>
-      <c r="H49" s="48" t="s">
+      <c r="H49" s="49" t="s">
         <v>337</v>
       </c>
-      <c r="I49" s="48" t="s">
+      <c r="I49" s="49" t="s">
         <v>338</v>
       </c>
-      <c r="J49" s="4"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-    </row>
-    <row r="50" spans="1:37" ht="62.5">
-      <c r="A50" s="16">
+      <c r="J49" s="49" t="s">
+        <v>339</v>
+      </c>
+      <c r="K49" s="5"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
+      <c r="R49" s="5"/>
+      <c r="S49" s="5"/>
+    </row>
+    <row r="50" spans="1:38" ht="62.5">
+      <c r="A50" s="17">
         <v>46085</v>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="17">
         <v>46077</v>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="E50" s="51" t="s">
+      <c r="C50" s="17"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="F50" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="G50" s="48" t="s">
-        <v>311</v>
-      </c>
-      <c r="H50" s="48" t="s">
+      <c r="F50" s="52" t="s">
         <v>341</v>
       </c>
-      <c r="I50" s="48"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-    </row>
-    <row r="51" spans="1:37" ht="42">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D51" s="4" t="s">
+      <c r="G50" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="H50" s="49" t="s">
+        <v>312</v>
+      </c>
+      <c r="I50" s="49" t="s">
         <v>342</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="J50" s="49"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
+      <c r="R50" s="5"/>
+      <c r="S50" s="5"/>
+    </row>
+    <row r="51" spans="1:38" ht="42">
+      <c r="A51" s="5"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="F51" s="43" t="s">
+      <c r="F51" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="G51" s="39" t="s">
+      <c r="G51" s="44" t="s">
         <v>345</v>
       </c>
-      <c r="H51" s="7" t="s">
+      <c r="H51" s="40" t="s">
         <v>346</v>
       </c>
-      <c r="I51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R51" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="52" spans="1:37" ht="38">
-      <c r="A52" s="16">
+      <c r="I51" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q51" s="5"/>
+      <c r="R51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S51" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:38" ht="38">
+      <c r="A52" s="17">
         <v>46086</v>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="17">
         <v>46077</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="E52" s="4" t="s">
+      <c r="C52" s="17"/>
+      <c r="D52" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="F52" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" s="15" t="s">
         <v>350</v>
       </c>
-      <c r="H52" s="7" t="s">
+      <c r="H52" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="I52" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N52" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O52" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R52" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="53" spans="1:37" ht="75">
-      <c r="A53" s="4" t="s">
+      <c r="I52" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D53" s="4" t="s">
+      <c r="J52" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L52" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O52" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P52" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q52" s="5"/>
+      <c r="R52" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S52" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:38" ht="75">
+      <c r="A53" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="G53" s="53" t="s">
+      <c r="G53" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="H53" s="53" t="s">
+      <c r="H53" s="54" t="s">
         <v>357</v>
       </c>
-      <c r="I53" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N53" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O53" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R53" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="54" spans="1:37" ht="175">
-      <c r="A54" s="4"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D54" s="4" t="s">
+      <c r="I53" s="54" t="s">
         <v>358</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="J53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q53" s="5"/>
+      <c r="R53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S53" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:38" ht="150">
+      <c r="A54" s="5"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="F54" s="14" t="s">
+      <c r="F54" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G54" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="H54" s="53" t="s">
+      <c r="H54" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="I54" s="4" t="s">
+      <c r="I54" s="54" t="s">
         <v>363</v>
       </c>
-      <c r="J54" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="K54" s="53" t="s">
+      <c r="J54" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N54" s="27" t="s">
+      <c r="K54" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="L54" s="54" t="s">
         <v>365</v>
       </c>
-      <c r="O54" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R54" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="55" spans="1:37" ht="37.5">
-      <c r="A55" s="4"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D55" s="4" t="s">
+      <c r="M54" s="5"/>
+      <c r="N54" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O54" s="28" t="s">
         <v>366</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="P54" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q54" s="5"/>
+      <c r="R54" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S54" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:38" ht="37.5">
+      <c r="A55" s="5"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="G55" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="H55" s="4" t="s">
+      <c r="H55" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="I55" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O55" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R55" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="56" spans="1:37" ht="42">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D56" s="4" t="s">
+      <c r="I55" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="J55" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L55" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O55" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P55" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q55" s="5"/>
+      <c r="R55" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S55" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:38" ht="42">
+      <c r="A56" s="5"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="F56" s="14" t="s">
+      <c r="F56" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="G56" s="36" t="s">
+      <c r="G56" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K56" s="4" t="s">
+      <c r="H56" s="37" t="s">
         <v>375</v>
       </c>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N56" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O56" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R56" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="57" spans="1:37" ht="70">
-      <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D57" s="4" t="s">
+      <c r="I56" s="5"/>
+      <c r="J56" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L56" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="M56" s="5"/>
+      <c r="N56" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O56" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P56" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q56" s="5"/>
+      <c r="R56" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S56" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:38" ht="70">
+      <c r="A57" s="5"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="G57" s="36" t="s">
+      <c r="G57" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="H57" s="4" t="s">
+      <c r="H57" s="37" t="s">
         <v>380</v>
       </c>
-      <c r="I57" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K57" s="24" t="s">
+      <c r="I57" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N57" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O57" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R57" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="58" spans="1:37" ht="50">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D58" s="4" t="s">
+      <c r="J57" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L57" s="25" t="s">
         <v>382</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="M57" s="5"/>
+      <c r="N57" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O57" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P57" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q57" s="5"/>
+      <c r="R57" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S57" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:38" ht="50">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="F58" s="14" t="s">
+      <c r="F58" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="G58" s="54" t="s">
+      <c r="G58" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="H58" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="I58" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="J58" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="K58" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="L58" s="54"/>
-      <c r="M58" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="N58" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O58" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P58" s="4"/>
-      <c r="Q58" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="R58" s="54" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="59" spans="1:37" ht="37.5">
-      <c r="A59" s="4"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D59" s="4" t="s">
+      <c r="H58" s="55" t="s">
         <v>386</v>
       </c>
-      <c r="E59" s="4"/>
-      <c r="F59" s="14" t="s">
+      <c r="I58" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="J58" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="K58" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="L58" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="M58" s="55"/>
+      <c r="N58" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="O58" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P58" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q58" s="5"/>
+      <c r="R58" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="S58" s="55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:38" ht="37.5">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>387</v>
       </c>
+      <c r="F59" s="5"/>
       <c r="G59" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="H59" s="4" t="s">
+      <c r="H59" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="I59" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="J59" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="K59" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="L59" s="54"/>
-      <c r="M59" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="N59" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="O59" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="P59" s="54"/>
-      <c r="Q59" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="R59" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="AK59" s="55"/>
-    </row>
-    <row r="60" spans="1:37" ht="28">
-      <c r="A60" s="4"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D60" s="4" t="s">
+      <c r="I59" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="J59" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="K59" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="L59" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="M59" s="55"/>
+      <c r="N59" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="O59" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="P59" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q59" s="55"/>
+      <c r="R59" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="S59" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL59" s="56"/>
+    </row>
+    <row r="60" spans="1:38" ht="28">
+      <c r="A60" s="5"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="G60" s="36" t="s">
+      <c r="G60" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="H60" s="36" t="s">
+      <c r="H60" s="37" t="s">
         <v>394</v>
       </c>
-      <c r="I60" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N60" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O60" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P60" s="4"/>
-      <c r="Q60" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R60" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="61" spans="1:37" ht="38">
-      <c r="A61" s="16">
+      <c r="I60" s="37" t="s">
+        <v>395</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q60" s="5"/>
+      <c r="R60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S60" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:38" ht="25.5">
+      <c r="A61" s="17">
         <v>46086</v>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="17">
         <v>46080</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="E61" s="4" t="s">
+      <c r="C61" s="17"/>
+      <c r="D61" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F61" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="G61" s="4" t="s">
+      <c r="G61" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="H61" s="24" t="s">
+      <c r="H61" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="I61" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N61" s="4" t="s">
+      <c r="J61" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L61" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M61" s="95" t="s">
+        <v>562</v>
+      </c>
+      <c r="N61" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O61" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="O61" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R61" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="62" spans="1:37" ht="50.5">
-      <c r="A62" s="16">
+      <c r="P61" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q61" s="5"/>
+      <c r="R61" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S61" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:38" ht="50.5">
+      <c r="A62" s="17">
         <v>46085</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="17">
         <v>46077</v>
       </c>
-      <c r="C62" s="56" t="s">
-        <v>18</v>
-      </c>
+      <c r="C62" s="17"/>
       <c r="D62" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="58" t="s">
         <v>401</v>
       </c>
-      <c r="E62" s="56" t="s">
+      <c r="F62" s="57" t="s">
         <v>402</v>
       </c>
-      <c r="F62" s="58" t="s">
+      <c r="G62" s="59" t="s">
         <v>403</v>
       </c>
-      <c r="G62" s="59" t="s">
+      <c r="H62" s="60" t="s">
         <v>404</v>
       </c>
-      <c r="H62" s="56" t="s">
+      <c r="I62" s="57" t="s">
         <v>405</v>
       </c>
-      <c r="I62" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="J62" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="K62" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="L62" s="93"/>
-      <c r="M62" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="N62" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="O62" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="P62" s="56"/>
-      <c r="Q62" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="R62" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="S62" s="60"/>
-      <c r="T62" s="60"/>
-      <c r="U62" s="60"/>
-      <c r="V62" s="60"/>
-      <c r="W62" s="60"/>
-      <c r="X62" s="60"/>
-      <c r="Y62" s="60"/>
-      <c r="Z62" s="60"/>
-      <c r="AA62" s="60"/>
-      <c r="AB62" s="60"/>
-      <c r="AC62" s="60"/>
-      <c r="AD62" s="60"/>
-      <c r="AE62" s="60"/>
-      <c r="AF62" s="60"/>
-      <c r="AG62" s="60"/>
-      <c r="AH62" s="60"/>
-      <c r="AI62" s="60"/>
-      <c r="AJ62" s="60"/>
-      <c r="AK62" s="60"/>
-    </row>
-    <row r="63" spans="1:37" ht="88">
-      <c r="A63" s="16">
-        <v>46086</v>
-      </c>
-      <c r="B63" s="16">
-        <v>46078</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D63" s="4" t="s">
+      <c r="J62" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="K62" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="L62" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="M62" s="57"/>
+      <c r="N62" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="O62" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="P62" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q62" s="57"/>
+      <c r="R62" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="S62" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="T62" s="61"/>
+      <c r="U62" s="61"/>
+      <c r="V62" s="61"/>
+      <c r="W62" s="61"/>
+      <c r="X62" s="61"/>
+      <c r="Y62" s="61"/>
+      <c r="Z62" s="61"/>
+      <c r="AA62" s="61"/>
+      <c r="AB62" s="61"/>
+      <c r="AC62" s="61"/>
+      <c r="AD62" s="61"/>
+      <c r="AE62" s="61"/>
+      <c r="AF62" s="61"/>
+      <c r="AG62" s="61"/>
+      <c r="AH62" s="61"/>
+      <c r="AI62" s="61"/>
+      <c r="AJ62" s="61"/>
+      <c r="AK62" s="61"/>
+      <c r="AL62" s="61"/>
+    </row>
+    <row r="63" spans="1:38" ht="75.5">
+      <c r="B63" s="17">
+        <v>46085</v>
+      </c>
+      <c r="C63" s="42">
+        <v>3</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="F63" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="F63" s="14" t="s">
+      <c r="G63" s="15" t="s">
         <v>408</v>
       </c>
-      <c r="G63" s="15" t="s">
+      <c r="H63" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="H63" s="4" t="s">
+      <c r="I63" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="I63" s="4" t="s">
+      <c r="J63" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="J63" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K63" s="4" t="s">
+      <c r="K63" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L63" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N63" s="4" t="s">
+      <c r="M63" s="5"/>
+      <c r="N63" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O63" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="O63" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P63" s="4"/>
-      <c r="Q63" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R63" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="64" spans="1:37" ht="50.5">
-      <c r="A64" s="16">
+      <c r="P63" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q63" s="5"/>
+      <c r="R63" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S63" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:38" ht="50.5">
+      <c r="A64" s="17"/>
+      <c r="B64" s="17">
         <v>46085</v>
       </c>
-      <c r="B64" s="16">
+      <c r="C64" s="42">
+        <v>3</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="G64" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="H64" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="I64" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K64" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L64" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O64" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P64" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q64" s="5"/>
+      <c r="R64" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S64" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:38" ht="28">
+      <c r="A65" s="17">
+        <v>46085</v>
+      </c>
+      <c r="B65" s="17">
         <v>46077</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C65" s="17"/>
+      <c r="D65" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="G65" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="H65" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="I65" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="F64" s="14" t="s">
-        <v>416</v>
-      </c>
-      <c r="G64" s="36" t="s">
-        <v>417</v>
-      </c>
-      <c r="H64" s="36" t="s">
-        <v>418</v>
-      </c>
-      <c r="I64" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N64" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O64" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P64" s="4"/>
-      <c r="Q64" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R64" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="65" spans="1:37" ht="28">
-      <c r="A65" s="16">
+      <c r="J65" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L65" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O65" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P65" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q65" s="5"/>
+      <c r="R65" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S65" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:38" ht="28">
+      <c r="A66" s="17">
         <v>46085</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B66" s="17">
         <v>46077</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="F65" s="14" t="s">
-        <v>421</v>
-      </c>
-      <c r="G65" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="H65" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="I65" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K65" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N65" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O65" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P65" s="4"/>
-      <c r="Q65" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R65" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="66" spans="1:37" ht="28">
-      <c r="A66" s="16">
+      <c r="C66" s="17"/>
+      <c r="D66" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="G66" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="H66" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L66" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O66" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P66" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q66" s="5"/>
+      <c r="R66" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S66" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:38" ht="38">
+      <c r="A67" s="17">
         <v>46085</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B67" s="17">
         <v>46077</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="F66" s="14" t="s">
-        <v>425</v>
-      </c>
-      <c r="G66" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K66" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N66" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O66" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R66" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="67" spans="1:37" ht="38">
-      <c r="A67" s="16">
-        <v>46085</v>
-      </c>
-      <c r="B67" s="16">
+      <c r="C67" s="17"/>
+      <c r="D67" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="G67" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="H67" s="37" t="s">
+        <v>431</v>
+      </c>
+      <c r="I67" s="37" t="s">
+        <v>432</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L67" s="5"/>
+      <c r="M67" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="N67" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O67" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P67" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q67" s="5"/>
+      <c r="R67" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S67" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" spans="1:38" ht="88">
+      <c r="A68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="G68" s="62" t="s">
+        <v>436</v>
+      </c>
+      <c r="H68" s="55" t="s">
+        <v>437</v>
+      </c>
+      <c r="I68" s="55"/>
+      <c r="J68" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K68" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L68" s="9"/>
+      <c r="M68" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="N68" s="9"/>
+      <c r="O68" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="P68" s="9"/>
+      <c r="Q68" s="9"/>
+      <c r="R68" s="9"/>
+      <c r="S68" s="9"/>
+      <c r="T68" s="63"/>
+      <c r="U68" s="63"/>
+      <c r="V68" s="63"/>
+      <c r="W68" s="63"/>
+      <c r="X68" s="63"/>
+      <c r="Y68" s="63"/>
+      <c r="Z68" s="63"/>
+      <c r="AA68" s="63"/>
+      <c r="AB68" s="63"/>
+      <c r="AC68" s="63"/>
+      <c r="AD68" s="63"/>
+      <c r="AE68" s="63"/>
+    </row>
+    <row r="69" spans="1:38" ht="25.5">
+      <c r="A69" s="64">
+        <v>46084</v>
+      </c>
+      <c r="B69" s="64">
         <v>46077</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="F67" s="14" t="s">
-        <v>430</v>
-      </c>
-      <c r="G67" s="36" t="s">
-        <v>431</v>
-      </c>
-      <c r="H67" s="36" t="s">
-        <v>432</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J67" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="M67" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N67" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O67" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P67" s="4"/>
-      <c r="Q67" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R67" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="68" spans="1:37" ht="88">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>434</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="F68" s="61" t="s">
-        <v>436</v>
-      </c>
-      <c r="G68" s="54" t="s">
-        <v>437</v>
-      </c>
-      <c r="H68" s="54"/>
-      <c r="I68" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J68" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8" t="s">
-        <v>438</v>
-      </c>
-      <c r="M68" s="8"/>
-      <c r="N68" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="O68" s="8"/>
-      <c r="P68" s="8"/>
-      <c r="Q68" s="8"/>
-      <c r="R68" s="8"/>
-      <c r="S68" s="62"/>
-      <c r="T68" s="62"/>
-      <c r="U68" s="62"/>
-      <c r="V68" s="62"/>
-      <c r="W68" s="62"/>
-      <c r="X68" s="62"/>
-      <c r="Y68" s="62"/>
-      <c r="Z68" s="62"/>
-      <c r="AA68" s="62"/>
-      <c r="AB68" s="62"/>
-      <c r="AC68" s="62"/>
-      <c r="AD68" s="62"/>
-    </row>
-    <row r="69" spans="1:37" ht="25.5">
-      <c r="A69" s="63">
-        <v>46084</v>
-      </c>
-      <c r="B69" s="63">
-        <v>46077</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D69" s="8" t="s">
+      <c r="C69" s="64"/>
+      <c r="D69" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="F69" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="G69" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="G69" s="64" t="s">
+      <c r="H69" s="94" t="s">
         <v>443</v>
       </c>
-      <c r="H69" s="64"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4" t="s">
+      <c r="I69" s="93"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
-      <c r="Q69" s="4"/>
-      <c r="R69" s="4"/>
-    </row>
-    <row r="70" spans="1:37" ht="38">
-      <c r="A70" s="63">
+      <c r="P69" s="5"/>
+      <c r="Q69" s="5"/>
+      <c r="R69" s="5"/>
+      <c r="S69" s="5"/>
+    </row>
+    <row r="70" spans="1:38" ht="38">
+      <c r="A70" s="64">
         <f>B70+5</f>
         <v>46081</v>
       </c>
-      <c r="B70" s="63">
+      <c r="B70" s="64">
         <v>46076</v>
       </c>
-      <c r="C70" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D70" s="8" t="s">
+      <c r="C70" s="64"/>
+      <c r="D70" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E70" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="F70" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="F70" s="61" t="s">
+      <c r="G70" s="62" t="s">
         <v>447</v>
       </c>
-      <c r="G70" s="65" t="s">
+      <c r="H70" s="66" t="s">
         <v>448</v>
       </c>
-      <c r="H70" s="8" t="s">
+      <c r="I70" s="9" t="s">
         <v>449</v>
       </c>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4"/>
-      <c r="L70" s="4"/>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4"/>
-      <c r="O70" s="4"/>
-      <c r="P70" s="4"/>
-      <c r="Q70" s="4"/>
-      <c r="R70" s="4"/>
-    </row>
-    <row r="71" spans="1:37" ht="50.5">
-      <c r="A71" s="66">
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="5"/>
+      <c r="Q70" s="5"/>
+      <c r="R70" s="5"/>
+      <c r="S70" s="5"/>
+    </row>
+    <row r="71" spans="1:38" ht="50.5">
+      <c r="A71" s="67">
         <v>46085</v>
       </c>
-      <c r="B71" s="56"/>
-      <c r="C71" s="56" t="s">
-        <v>18</v>
-      </c>
-      <c r="D71" s="67" t="s">
+      <c r="B71" s="57"/>
+      <c r="C71" s="57"/>
+      <c r="D71" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="E71" s="68" t="s">
         <v>450</v>
       </c>
-      <c r="E71" s="67" t="s">
+      <c r="F71" s="68" t="s">
         <v>451</v>
       </c>
-      <c r="F71" s="68" t="s">
+      <c r="G71" s="69" t="s">
         <v>452</v>
       </c>
-      <c r="G71" s="69" t="s">
+      <c r="H71" s="70" t="s">
         <v>453</v>
       </c>
-      <c r="H71" s="56" t="s">
+      <c r="I71" s="57" t="s">
         <v>454</v>
       </c>
-      <c r="I71" s="56" t="s">
+      <c r="J71" s="57" t="s">
         <v>455</v>
       </c>
-      <c r="J71" s="56"/>
-      <c r="K71" s="67" t="s">
+      <c r="K71" s="57"/>
+      <c r="L71" s="68" t="s">
         <v>456</v>
       </c>
-      <c r="L71" s="56"/>
-      <c r="M71" s="56"/>
-      <c r="N71" s="56"/>
-      <c r="O71" s="56"/>
-      <c r="P71" s="56"/>
-      <c r="Q71" s="56"/>
-      <c r="R71" s="56"/>
-      <c r="S71" s="60"/>
-      <c r="T71" s="60"/>
-      <c r="U71" s="60"/>
-      <c r="V71" s="60"/>
-      <c r="W71" s="60"/>
-      <c r="X71" s="60"/>
-      <c r="Y71" s="60"/>
-      <c r="Z71" s="60"/>
-      <c r="AA71" s="60"/>
-      <c r="AB71" s="60"/>
-      <c r="AC71" s="60"/>
-      <c r="AD71" s="60"/>
-      <c r="AE71" s="60"/>
-      <c r="AF71" s="60"/>
-      <c r="AG71" s="60"/>
-      <c r="AH71" s="60"/>
-      <c r="AI71" s="60"/>
-      <c r="AJ71" s="60"/>
-      <c r="AK71" s="60"/>
-    </row>
-    <row r="72" spans="1:37" ht="50.5">
-      <c r="A72" s="63">
+      <c r="M71" s="57"/>
+      <c r="N71" s="57"/>
+      <c r="O71" s="57"/>
+      <c r="P71" s="57"/>
+      <c r="Q71" s="57"/>
+      <c r="R71" s="57"/>
+      <c r="S71" s="57"/>
+      <c r="T71" s="61"/>
+      <c r="U71" s="61"/>
+      <c r="V71" s="61"/>
+      <c r="W71" s="61"/>
+      <c r="X71" s="61"/>
+      <c r="Y71" s="61"/>
+      <c r="Z71" s="61"/>
+      <c r="AA71" s="61"/>
+      <c r="AB71" s="61"/>
+      <c r="AC71" s="61"/>
+      <c r="AD71" s="61"/>
+      <c r="AE71" s="61"/>
+      <c r="AF71" s="61"/>
+      <c r="AG71" s="61"/>
+      <c r="AH71" s="61"/>
+      <c r="AI71" s="61"/>
+      <c r="AJ71" s="61"/>
+      <c r="AK71" s="61"/>
+      <c r="AL71" s="61"/>
+    </row>
+    <row r="72" spans="1:38" ht="50.5">
+      <c r="A72" s="64">
         <f>B72+5</f>
         <v>46076</v>
       </c>
-      <c r="B72" s="63">
+      <c r="B72" s="64">
         <v>46071</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D72" s="4" t="s">
+      <c r="C72" s="64"/>
+      <c r="D72" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E72" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="F72" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="F72" s="14" t="s">
+      <c r="G72" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="G72" s="15" t="s">
+      <c r="H72" s="16" t="s">
         <v>460</v>
       </c>
-      <c r="H72" s="27" t="s">
+      <c r="I72" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="I72" s="4" t="s">
+      <c r="J72" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="J72" s="4"/>
-      <c r="K72" s="24"/>
-      <c r="L72" s="70">
+      <c r="K72" s="5"/>
+      <c r="L72" s="25"/>
+      <c r="M72" s="71">
         <v>46071.666666666664</v>
       </c>
-      <c r="M72" s="4"/>
-      <c r="N72" s="4"/>
-      <c r="O72" s="4"/>
-      <c r="P72" s="4"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
-    </row>
-    <row r="73" spans="1:37" ht="70">
-      <c r="A73" s="4"/>
-      <c r="B73" s="71">
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="5"/>
+      <c r="Q72" s="5"/>
+      <c r="R72" s="5"/>
+      <c r="S72" s="5"/>
+    </row>
+    <row r="73" spans="1:38" ht="70">
+      <c r="A73" s="5"/>
+      <c r="B73" s="72">
         <v>46077</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D73" s="8" t="s">
+      <c r="C73" s="72"/>
+      <c r="D73" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E73" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="F73" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="F73" s="72" t="s">
+      <c r="G73" s="73" t="s">
         <v>465</v>
       </c>
-      <c r="G73" s="54" t="s">
+      <c r="H73" s="55" t="s">
         <v>466</v>
       </c>
-      <c r="H73" s="8" t="s">
+      <c r="I73" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="I73" s="8" t="s">
+      <c r="J73" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="J73" s="56" t="s">
+      <c r="K73" s="57" t="s">
         <v>469</v>
       </c>
-      <c r="K73" s="8" t="s">
+      <c r="L73" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8"/>
-      <c r="N73" s="8"/>
-      <c r="O73" s="8"/>
-      <c r="P73" s="8"/>
-      <c r="Q73" s="8"/>
-      <c r="R73" s="8"/>
-      <c r="S73" s="62"/>
-      <c r="T73" s="62"/>
-      <c r="U73" s="62"/>
-      <c r="V73" s="62"/>
-      <c r="W73" s="62"/>
-      <c r="X73" s="62"/>
-      <c r="Y73" s="62"/>
-      <c r="Z73" s="62"/>
-      <c r="AA73" s="62"/>
-      <c r="AB73" s="62"/>
-      <c r="AC73" s="62"/>
-    </row>
-    <row r="74" spans="1:37" ht="38">
-      <c r="A74" s="63">
+      <c r="M73" s="9"/>
+      <c r="N73" s="9"/>
+      <c r="O73" s="9"/>
+      <c r="P73" s="9"/>
+      <c r="Q73" s="9"/>
+      <c r="R73" s="9"/>
+      <c r="S73" s="9"/>
+      <c r="T73" s="63"/>
+      <c r="U73" s="63"/>
+      <c r="V73" s="63"/>
+      <c r="W73" s="63"/>
+      <c r="X73" s="63"/>
+      <c r="Y73" s="63"/>
+      <c r="Z73" s="63"/>
+      <c r="AA73" s="63"/>
+      <c r="AB73" s="63"/>
+      <c r="AC73" s="63"/>
+      <c r="AD73" s="63"/>
+    </row>
+    <row r="74" spans="1:38" ht="38">
+      <c r="A74" s="64">
         <f t="shared" ref="A74:A75" si="0">B74+5</f>
         <v>46081</v>
       </c>
-      <c r="B74" s="63">
+      <c r="B74" s="64">
         <v>46076</v>
       </c>
-      <c r="C74" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="D74" s="27" t="s">
+      <c r="C74" s="64"/>
+      <c r="D74" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="E74" s="28" t="s">
         <v>471</v>
       </c>
-      <c r="E74" s="27" t="s">
+      <c r="F74" s="28" t="s">
         <v>472</v>
       </c>
-      <c r="F74" s="73" t="s">
+      <c r="G74" s="74" t="s">
         <v>473</v>
       </c>
-      <c r="G74" s="15" t="s">
+      <c r="H74" s="16" t="s">
         <v>474</v>
       </c>
-      <c r="H74" s="27" t="s">
+      <c r="I74" s="28" t="s">
         <v>475</v>
       </c>
-      <c r="I74" s="27" t="s">
+      <c r="J74" s="28" t="s">
         <v>476</v>
       </c>
-      <c r="J74" s="27"/>
-      <c r="K74" s="27"/>
-      <c r="L74" s="27"/>
-      <c r="M74" s="27"/>
-      <c r="N74" s="27"/>
-      <c r="O74" s="27"/>
-      <c r="P74" s="27"/>
-      <c r="Q74" s="27"/>
-      <c r="R74" s="27"/>
-    </row>
-    <row r="75" spans="1:37" ht="50.5">
-      <c r="A75" s="63">
+      <c r="K74" s="28"/>
+      <c r="L74" s="28"/>
+      <c r="M74" s="28"/>
+      <c r="N74" s="28"/>
+      <c r="O74" s="28"/>
+      <c r="P74" s="28"/>
+      <c r="Q74" s="28"/>
+      <c r="R74" s="28"/>
+      <c r="S74" s="28"/>
+    </row>
+    <row r="75" spans="1:38" ht="50.5">
+      <c r="A75" s="64">
         <f t="shared" si="0"/>
         <v>46081</v>
       </c>
-      <c r="B75" s="63">
+      <c r="B75" s="64">
         <v>46076</v>
       </c>
-      <c r="C75" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="D75" s="27" t="s">
+      <c r="C75" s="64"/>
+      <c r="D75" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="E75" s="28" t="s">
         <v>477</v>
       </c>
-      <c r="E75" s="27" t="s">
+      <c r="F75" s="28" t="s">
         <v>478</v>
       </c>
-      <c r="F75" s="74" t="s">
+      <c r="G75" s="75" t="s">
         <v>479</v>
       </c>
-      <c r="G75" s="36" t="s">
+      <c r="H75" s="37" t="s">
         <v>480</v>
       </c>
-      <c r="H75" s="36" t="s">
+      <c r="I75" s="37" t="s">
         <v>481</v>
       </c>
-      <c r="I75" s="27" t="s">
+      <c r="J75" s="28" t="s">
         <v>482</v>
       </c>
-      <c r="J75" s="27"/>
-      <c r="K75" s="27"/>
-      <c r="L75" s="27"/>
-      <c r="M75" s="27"/>
-      <c r="N75" s="27"/>
-      <c r="O75" s="27"/>
-      <c r="P75" s="27"/>
-      <c r="Q75" s="27"/>
-      <c r="R75" s="27"/>
-    </row>
-    <row r="76" spans="1:37" ht="112.5">
-      <c r="A76" s="16">
+      <c r="K75" s="28"/>
+      <c r="L75" s="28"/>
+      <c r="M75" s="28"/>
+      <c r="N75" s="28"/>
+      <c r="O75" s="28"/>
+      <c r="P75" s="28"/>
+      <c r="Q75" s="28"/>
+      <c r="R75" s="28"/>
+      <c r="S75" s="28"/>
+    </row>
+    <row r="76" spans="1:38" ht="112.5">
+      <c r="A76" s="17">
         <v>46087</v>
       </c>
-      <c r="B76" s="63">
+      <c r="B76" s="64">
         <v>46079</v>
       </c>
-      <c r="C76" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="D76" s="75" t="s">
+      <c r="C76" s="64"/>
+      <c r="D76" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E76" s="76" t="s">
         <v>483</v>
       </c>
-      <c r="E76" s="75" t="s">
+      <c r="F76" s="76" t="s">
         <v>484</v>
       </c>
-      <c r="F76" s="76" t="s">
+      <c r="G76" s="77" t="s">
         <v>485</v>
       </c>
-      <c r="G76" s="75" t="s">
+      <c r="H76" s="76" t="s">
         <v>486</v>
       </c>
-      <c r="H76" s="77" t="s">
+      <c r="I76" s="78" t="s">
         <v>487</v>
       </c>
-      <c r="I76" s="27"/>
-      <c r="J76" s="27"/>
-      <c r="K76" s="27"/>
-      <c r="L76" s="27"/>
-      <c r="M76" s="27"/>
-      <c r="N76" s="27"/>
-      <c r="O76" s="27"/>
-      <c r="P76" s="27"/>
-      <c r="Q76" s="27"/>
-      <c r="R76" s="27"/>
-    </row>
-    <row r="77" spans="1:37" ht="14">
-      <c r="A77" s="51"/>
-      <c r="B77" s="51"/>
-      <c r="C77" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="D77" s="51" t="s">
+      <c r="J76" s="28"/>
+      <c r="K76" s="28"/>
+      <c r="L76" s="28"/>
+      <c r="M76" s="28"/>
+      <c r="N76" s="28"/>
+      <c r="O76" s="28"/>
+      <c r="P76" s="28"/>
+      <c r="Q76" s="28"/>
+      <c r="R76" s="28"/>
+      <c r="S76" s="28"/>
+    </row>
+    <row r="77" spans="1:38" ht="14">
+      <c r="A77" s="52"/>
+      <c r="B77" s="52"/>
+      <c r="C77" s="52"/>
+      <c r="D77" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="E77" s="52" t="s">
         <v>488</v>
       </c>
-      <c r="E77" s="51" t="s">
+      <c r="F77" s="52" t="s">
         <v>489</v>
       </c>
-      <c r="F77" s="78" t="s">
+      <c r="G77" s="79" t="s">
         <v>490</v>
       </c>
-      <c r="G77" s="64" t="s">
+      <c r="H77" s="65" t="s">
         <v>491</v>
       </c>
-      <c r="H77" s="79" t="s">
+      <c r="I77" s="80" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="78" spans="1:37" ht="14">
-      <c r="A78" s="63">
+    <row r="78" spans="1:38" ht="14">
+      <c r="A78" s="64">
         <v>46086</v>
       </c>
-      <c r="B78" s="63">
+      <c r="B78" s="64">
         <v>46077</v>
       </c>
-      <c r="C78" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="D78" s="51" t="s">
+      <c r="C78" s="64"/>
+      <c r="D78" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" s="52" t="s">
         <v>493</v>
       </c>
-      <c r="E78" s="51" t="s">
+      <c r="F78" s="52" t="s">
         <v>494</v>
       </c>
-      <c r="F78" s="78" t="s">
+      <c r="G78" s="79" t="s">
         <v>495</v>
       </c>
-      <c r="G78" s="64" t="s">
+      <c r="H78" s="65" t="s">
         <v>496</v>
       </c>
-      <c r="H78" s="51" t="s">
+      <c r="I78" s="52" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="79" spans="1:37" ht="14">
-      <c r="A79" s="63">
+    <row r="79" spans="1:38" ht="14">
+      <c r="A79" s="64">
         <v>46086</v>
       </c>
-      <c r="B79" s="63">
+      <c r="B79" s="64">
         <v>46078</v>
       </c>
-      <c r="C79" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="D79" s="51" t="s">
+      <c r="C79" s="64"/>
+      <c r="D79" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="E79" s="52" t="s">
         <v>498</v>
       </c>
-      <c r="E79" s="51" t="s">
+      <c r="F79" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="F79" s="78" t="s">
+      <c r="G79" s="79" t="s">
         <v>500</v>
       </c>
-      <c r="G79" s="64" t="s">
+      <c r="H79" s="65" t="s">
         <v>501</v>
       </c>
-      <c r="H79" s="51" t="s">
+      <c r="I79" s="52" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="80" spans="1:37" ht="14">
-      <c r="A80" s="63">
+    <row r="80" spans="1:38" ht="14">
+      <c r="A80" s="64">
         <v>46087</v>
       </c>
-      <c r="B80" s="63">
+      <c r="B80" s="64">
         <v>46079</v>
       </c>
-      <c r="C80" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="D80" s="51" t="s">
+      <c r="C80" s="64"/>
+      <c r="D80" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="E80" s="52" t="s">
         <v>503</v>
       </c>
-      <c r="E80" s="51" t="s">
+      <c r="F80" s="52" t="s">
         <v>504</v>
       </c>
-      <c r="F80" s="51" t="s">
+      <c r="G80" s="52" t="s">
         <v>503</v>
       </c>
-      <c r="G80" s="64" t="s">
+      <c r="H80" s="65" t="s">
         <v>505</v>
       </c>
-      <c r="H80" s="64"/>
-      <c r="I80" s="51" t="s">
+      <c r="I80" s="65"/>
+      <c r="J80" s="52" t="s">
         <v>506</v>
       </c>
-      <c r="L80" s="60" t="s">
+      <c r="M80" s="61" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="14">
-      <c r="A81" s="63">
+    <row r="81" spans="1:13" ht="14">
+      <c r="A81" s="64">
         <v>46087</v>
       </c>
-      <c r="B81" s="63">
+      <c r="B81" s="64">
         <v>46080</v>
       </c>
-      <c r="C81" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="D81" s="51" t="s">
+      <c r="C81" s="64"/>
+      <c r="D81" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="E81" s="52" t="s">
         <v>508</v>
       </c>
-      <c r="E81" s="51" t="s">
+      <c r="F81" s="52" t="s">
         <v>509</v>
       </c>
-      <c r="F81" s="78" t="s">
+      <c r="G81" s="79" t="s">
         <v>510</v>
       </c>
-      <c r="G81" s="80" t="s">
+      <c r="H81" s="81" t="s">
         <v>511</v>
       </c>
-      <c r="H81" s="62" t="s">
+      <c r="I81" s="63" t="s">
         <v>512</v>
       </c>
-      <c r="L81" s="81" t="s">
+      <c r="M81" s="82" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="14">
-      <c r="A82" s="62"/>
-      <c r="B82" s="16">
+    <row r="82" spans="1:13" ht="14">
+      <c r="A82" s="63"/>
+      <c r="B82" s="17">
         <v>46080</v>
       </c>
-      <c r="C82" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="D82" s="62" t="s">
+      <c r="C82" s="17"/>
+      <c r="D82" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="E82" s="63" t="s">
         <v>514</v>
       </c>
-      <c r="E82" s="62" t="s">
+      <c r="F82" s="63" t="s">
         <v>515</v>
       </c>
-      <c r="F82" s="76" t="s">
+      <c r="G82" s="77" t="s">
         <v>516</v>
       </c>
-      <c r="G82" s="55" t="s">
+      <c r="H82" s="56" t="s">
         <v>517</v>
       </c>
-      <c r="H82" s="82"/>
-      <c r="K82" t="s">
+      <c r="I82" s="83"/>
+      <c r="L82" s="84" t="s">
         <v>518</v>
       </c>
-      <c r="L82" s="83"/>
-    </row>
-    <row r="83" spans="1:12" ht="14">
-      <c r="A83" s="62"/>
-      <c r="B83" s="16">
+    </row>
+    <row r="83" spans="1:13" ht="14">
+      <c r="A83" s="63"/>
+      <c r="B83" s="17">
         <v>46080</v>
       </c>
-      <c r="C83" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="D83" s="75" t="s">
+      <c r="C83" s="17"/>
+      <c r="D83" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="E83" s="76" t="s">
         <v>519</v>
       </c>
-      <c r="E83" s="62" t="s">
+      <c r="F83" s="63" t="s">
         <v>520</v>
       </c>
-      <c r="F83" s="76" t="s">
+      <c r="G83" s="77" t="s">
         <v>521</v>
       </c>
-      <c r="G83" s="84" t="s">
+      <c r="H83" s="85" t="s">
         <v>522</v>
       </c>
-      <c r="H83" s="62"/>
-      <c r="L83" s="85" t="s">
+      <c r="I83" s="63"/>
+      <c r="M83" s="86" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="26">
-      <c r="C84" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="D84" s="62" t="s">
+    <row r="84" spans="1:13" ht="26">
+      <c r="D84" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="E84" s="63" t="s">
         <v>524</v>
       </c>
-      <c r="E84" s="62" t="s">
+      <c r="F84" s="63" t="s">
         <v>525</v>
       </c>
-      <c r="F84" s="76" t="s">
+      <c r="G84" s="77" t="s">
         <v>526</v>
       </c>
-      <c r="G84" s="75" t="s">
+      <c r="H84" s="76" t="s">
         <v>527</v>
       </c>
-      <c r="H84" s="86" t="s">
+      <c r="I84" s="87" t="s">
         <v>528</v>
       </c>
-      <c r="I84" s="51" t="s">
+      <c r="J84" s="52" t="s">
         <v>529</v>
       </c>
-      <c r="L84" s="87" t="s">
+      <c r="M84" s="88" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="16">
-      <c r="C85" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="D85" s="62" t="s">
+    <row r="85" spans="1:13" ht="16">
+      <c r="D85" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="E85" s="63" t="s">
         <v>531</v>
       </c>
-      <c r="E85" s="62" t="s">
+      <c r="F85" s="63" t="s">
         <v>532</v>
       </c>
-      <c r="F85" s="76" t="s">
+      <c r="G85" s="77" t="s">
         <v>533</v>
       </c>
-      <c r="G85" s="55" t="s">
+      <c r="H85" s="56" t="s">
         <v>534</v>
       </c>
-      <c r="H85" s="55" t="s">
+      <c r="I85" s="56" t="s">
         <v>535</v>
       </c>
-      <c r="I85" s="88" t="s">
+      <c r="J85" s="89" t="s">
         <v>536</v>
       </c>
-      <c r="L85" s="89" t="s">
+      <c r="M85" s="90" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="14">
-      <c r="C86" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="D86" s="62" t="s">
+    <row r="86" spans="1:13" ht="14">
+      <c r="D86" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="E86" s="63" t="s">
         <v>538</v>
       </c>
-      <c r="E86" s="62" t="s">
+      <c r="F86" s="63" t="s">
         <v>539</v>
       </c>
-      <c r="F86" s="76" t="s">
+      <c r="G86" s="77" t="s">
         <v>540</v>
       </c>
-      <c r="G86" s="84" t="s">
+      <c r="H86" s="85" t="s">
         <v>541</v>
       </c>
-      <c r="H86" s="62" t="s">
+      <c r="I86" s="63" t="s">
         <v>542</v>
       </c>
-      <c r="I86" s="62" t="s">
+      <c r="J86" s="63" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="14">
-      <c r="C87" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="D87" s="62" t="s">
+    <row r="87" spans="1:13" ht="14">
+      <c r="D87" s="52" t="s">
+        <v>333</v>
+      </c>
+      <c r="E87" s="63" t="s">
         <v>544</v>
       </c>
-      <c r="E87" s="62" t="s">
+      <c r="F87" s="63" t="s">
         <v>545</v>
       </c>
-      <c r="F87" s="76" t="s">
+      <c r="G87" s="77" t="s">
         <v>546</v>
       </c>
-      <c r="G87" s="55" t="s">
+      <c r="H87" s="56" t="s">
         <v>547</v>
       </c>
-      <c r="H87" s="90" t="s">
+      <c r="I87" s="91" t="s">
         <v>548</v>
       </c>
-      <c r="I87" s="62" t="s">
+      <c r="J87" s="63" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="14">
-      <c r="C88" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="D88" s="62" t="s">
+    <row r="88" spans="1:13" ht="14">
+      <c r="D88" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="E88" s="63" t="s">
         <v>550</v>
       </c>
-      <c r="E88" s="62" t="s">
+      <c r="F88" s="63" t="s">
         <v>551</v>
       </c>
-      <c r="F88" s="76" t="s">
+      <c r="G88" s="77" t="s">
         <v>552</v>
       </c>
-      <c r="G88" s="84" t="s">
+      <c r="H88" s="85" t="s">
         <v>553</v>
       </c>
-      <c r="H88" s="51" t="s">
+      <c r="I88" s="52" t="s">
         <v>554</v>
       </c>
-      <c r="I88" s="85" t="s">
+      <c r="J88" s="86" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="14">
-      <c r="C89" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="D89" s="62" t="s">
+    <row r="89" spans="1:13" ht="14">
+      <c r="D89" s="52" t="s">
+        <v>333</v>
+      </c>
+      <c r="E89" s="63" t="s">
         <v>556</v>
       </c>
-      <c r="E89" s="62" t="s">
+      <c r="F89" s="63" t="s">
         <v>557</v>
       </c>
-      <c r="F89" s="76" t="s">
+      <c r="G89" s="77" t="s">
         <v>558</v>
       </c>
-      <c r="G89" s="55" t="s">
+      <c r="H89" s="56" t="s">
         <v>559</v>
       </c>
-      <c r="H89" s="88" t="s">
+      <c r="I89" s="89" t="s">
         <v>560</v>
       </c>
-      <c r="I89" s="88" t="s">
+      <c r="J89" s="89" t="s">
         <v>561</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D1003" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="1">
-    <mergeCell ref="G37:H37"/>
+  <autoFilter ref="E1:E1003" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <mergeCells count="2">
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H69:I69"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="F5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="F6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="I6" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="F7" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="F8" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="F9" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="F10" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="F11" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="F12" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="F13" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="F14" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="F15" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F16" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="F17" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="F18" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="F19" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="F20" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="F21" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="F22" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="F23" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="F24" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="F25" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="F26" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="F27" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="F28" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="F29" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="F31" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="F32" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="F33" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="F34" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="F35" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="G35" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="F36" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="F37" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="F38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="F39" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="F40" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="F41" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="F42" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="F43" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="F44" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="F45" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="F46" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="G46" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="F47" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="F48" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="F49" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="D50" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="F50" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="F51" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="G51" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="F52" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="F53" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="F54" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="F55" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="F56" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="F57" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="F58" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="F59" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="F60" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="F61" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="D62" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="F62" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="F63" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="F64" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="F65" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="F66" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="F67" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="F68" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="F69" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="F70" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="F71" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="F72" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="F73" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="F74" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="F75" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="F76" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="F77" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="F78" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="F79" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="F81" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="F82" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="F83" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="F84" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="F85" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="F86" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="F87" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="F88" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="F89" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="G3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="G4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="G5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="G6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="J6" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="G7" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="G8" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="G9" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="G10" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="G11" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="G12" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="G13" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="G14" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="G15" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="G16" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="G17" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="G18" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="G19" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="G20" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="G21" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="G22" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="G23" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="G24" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="G25" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="G26" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="G27" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="G28" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="G29" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="G31" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="G32" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="G33" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="G34" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="G35" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="H35" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="G36" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="G37" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="G38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="G39" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="G40" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="G41" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="G42" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="G43" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="G44" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="G45" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="G46" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="H46" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="G47" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="G48" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="G49" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="E50" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="G50" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="G51" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="H51" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="G52" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="G53" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="G54" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="G55" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="G56" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="G57" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="G58" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="G59" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="G60" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="G61" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="E62" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="G62" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="G63" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="G64" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="G65" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="G66" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="G67" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="G68" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="G69" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="G70" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="G71" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="G72" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="G73" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="G74" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="G75" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="G76" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="G77" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="G78" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="G79" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="G81" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="G82" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="G83" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="G84" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="G85" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="G86" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="G87" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="G88" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="G89" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/dashboard/Dashboard.xlsx
+++ b/backend/dashboard/Dashboard.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Engineering\New folder\Company_details\dashboard\backend\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0BC294-1CDD-4946-8E5B-4780B7F28D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72897499-1C22-422A-879D-102D4886CF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Filtered" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$E$1:$E$1003</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$F$1:$F$1003</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,13 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="563">
-  <si>
-    <t>Next Followup</t>
-  </si>
-  <si>
-    <t>Last Follow up date</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="581">
   <si>
     <t>No of follow ups</t>
   </si>
@@ -1558,6 +1553,9 @@
     <t>Mohammad Rafiuddin &lt;mohammad.rafiuddin@ceew.in&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">meet 05-03-2026 4pm </t>
+  </si>
+  <si>
     <t>11 Feb 2026 Requirement Discussed</t>
   </si>
   <si>
@@ -1706,7 +1704,13 @@
     <t>gujratgas.com</t>
   </si>
   <si>
-    <t>Naveen Sharma &lt;naveen.sharma@gujaratgas.com&gt;  +91 9824107045</t>
+    <t>Naveen Sharma &lt;naveen.sharma@gujaratgas.com&gt;  +91 9824107045 manish.dhroov@gujaratgas.com</t>
+  </si>
+  <si>
+    <t>Looped in manish.</t>
+  </si>
+  <si>
+    <t>Mail sent on March 11 requesting time.</t>
   </si>
   <si>
     <t>\</t>
@@ -1978,7 +1982,16 @@
     <t>Pranaya Sangvai &lt;pranaya.sangvai@samit.in&gt;</t>
   </si>
   <si>
+    <t>set call on 05-03-2026</t>
+  </si>
+  <si>
     <t>call on monday 3 march at 10:30 am</t>
+  </si>
+  <si>
+    <t xml:space="preserve">call 05-03-2026:
+They dont have any project for now,
+They needed for oil spills, geophysicals studies etc.
+When they will do such projects they will need us thus stay connected, </t>
   </si>
   <si>
     <t>WeGauge Pipeline Inspection &amp; Services Pvt. Ltd</t>
@@ -2097,7 +2110,52 @@
     <t xml:space="preserve">sent number </t>
   </si>
   <si>
-    <t xml:space="preserve">03/05/2026 4pm </t>
+    <t>trust signals</t>
+  </si>
+  <si>
+    <t>Communication Platform as a Service (CPaaS) / Messaging infrastructure</t>
+  </si>
+  <si>
+    <t>Imran Shaikh &lt;imran@trustsignal.io&gt;</t>
+  </si>
+  <si>
+    <t>Telecommunications / Enterprise communication systems</t>
+  </si>
+  <si>
+    <t>Rajesh Tuli &lt;rajeshtuli@coraltele.com&gt;</t>
+  </si>
+  <si>
+    <t>Flosil</t>
+  </si>
+  <si>
+    <t>Oil and Gas Equipment Services</t>
+  </si>
+  <si>
+    <t>flosil.com</t>
+  </si>
+  <si>
+    <t>arun@flosil.com</t>
+  </si>
+  <si>
+    <t>requested for porfile and will get back to us.</t>
+  </si>
+  <si>
+    <t>Decks sent on March 12</t>
+  </si>
+  <si>
+    <t>Follow_up 1</t>
+  </si>
+  <si>
+    <t>Follow_up 2</t>
+  </si>
+  <si>
+    <t>Follow_up 3</t>
+  </si>
+  <si>
+    <t>18/2/2026</t>
+  </si>
+  <si>
+    <t>03-09-2026 at 3pm</t>
   </si>
 </sst>
 </file>
@@ -2110,7 +2168,7 @@
     <numFmt numFmtId="166" formatCode="dd\-mm\-yy"/>
     <numFmt numFmtId="167" formatCode="d\ mmm\ yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="51">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2282,12 +2340,6 @@
       <name val="&quot;Google Sans&quot;"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
-      <name val="&quot;Google Sans&quot;"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Google Sans"/>
@@ -2346,12 +2398,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -2375,6 +2421,11 @@
       <sz val="10"/>
       <color rgb="FF222222"/>
       <name val="Verdana"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
@@ -2404,7 +2455,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2447,6 +2498,12 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF4CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2460,7 +2517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2608,44 +2665,39 @@
     <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2654,65 +2706,73 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="45" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="46" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2931,83 +2991,85 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AL89"/>
+  <dimension ref="A1:AM92"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="14.453125" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="18.6328125" customWidth="1"/>
-    <col min="7" max="7" width="19.453125" customWidth="1"/>
-    <col min="8" max="8" width="32.90625" customWidth="1"/>
-    <col min="9" max="9" width="25.36328125" customWidth="1"/>
-    <col min="10" max="10" width="30.26953125" customWidth="1"/>
-    <col min="11" max="11" width="21" customWidth="1"/>
-    <col min="12" max="13" width="21.453125" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="33.08984375" customWidth="1"/>
-    <col min="16" max="17" width="28.6328125" customWidth="1"/>
-    <col min="18" max="18" width="21.453125" customWidth="1"/>
+    <col min="1" max="5" width="14.453125" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="18.6328125" customWidth="1"/>
+    <col min="8" max="8" width="19.453125" customWidth="1"/>
+    <col min="9" max="9" width="32.90625" customWidth="1"/>
+    <col min="10" max="10" width="25.36328125" customWidth="1"/>
+    <col min="11" max="11" width="30.26953125" customWidth="1"/>
+    <col min="12" max="12" width="21" customWidth="1"/>
+    <col min="13" max="14" width="21.453125" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="33.08984375" customWidth="1"/>
+    <col min="17" max="18" width="28.6328125" customWidth="1"/>
+    <col min="19" max="19" width="21.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38">
+    <row r="1" spans="1:39" ht="26">
       <c r="A1" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="4"/>
       <c r="U1" s="4"/>
       <c r="V1" s="4"/>
       <c r="W1" s="4"/>
@@ -3026,395 +3088,403 @@
       <c r="AJ1" s="4"/>
       <c r="AK1" s="4"/>
       <c r="AL1" s="4"/>
-    </row>
-    <row r="2" spans="1:38" ht="15.75" customHeight="1">
+      <c r="AM1" s="4"/>
+    </row>
+    <row r="2" spans="1:39" ht="15.75" customHeight="1">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="H2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="I2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="J2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="K2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="L2" s="5"/>
+      <c r="M2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5" t="s">
+      <c r="N2" s="5"/>
+      <c r="O2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5" t="s">
+      <c r="R2" s="8"/>
+      <c r="S2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:38" ht="15.75" customHeight="1">
+      <c r="T2" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:39" ht="15.75" customHeight="1">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="H3" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="J3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="K3" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="5"/>
+        <v>25</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="N3" s="5"/>
-      <c r="O3" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="O3" s="5"/>
       <c r="P3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R3" s="5"/>
       <c r="S3" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:38">
+        <v>25</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39" ht="63">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
-      <c r="D4" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="I4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="J4" s="5"/>
+      <c r="K4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="L4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="8" t="s">
+      <c r="M4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:38" ht="15.75" customHeight="1">
+      <c r="T4" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" ht="15.75" customHeight="1">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
-      <c r="D5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="14" t="s">
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="I5" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="J5" s="5"/>
+      <c r="K5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="N5" s="5"/>
       <c r="O5" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5" t="s">
-        <v>42</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R5" s="5"/>
       <c r="S5" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:38" ht="15.75" customHeight="1">
+        <v>40</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" ht="15.75" customHeight="1">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="D6" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="J6" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="K6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="L6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="T6" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5" t="s">
+    </row>
+    <row r="7" spans="1:39" ht="38">
+      <c r="A7" s="5"/>
+      <c r="B7" s="17" t="s">
+        <v>579</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="S6" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="7" spans="1:38">
-      <c r="A7" s="5"/>
-      <c r="B7" s="17">
-        <v>46071</v>
-      </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="H7" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="J7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="N7" s="5"/>
+      <c r="O7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:38">
+      <c r="T7" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" ht="42">
       <c r="A8" s="5"/>
       <c r="B8" s="17">
         <v>46071</v>
       </c>
       <c r="C8" s="17"/>
-      <c r="D8" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="D8" s="17"/>
       <c r="E8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="I8" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="J8" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="K8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="N8" s="5"/>
+      <c r="O8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R8" s="5"/>
+      <c r="S8" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:38" ht="15.75" customHeight="1">
+      <c r="T8" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" ht="15.75" customHeight="1">
       <c r="A9" s="19"/>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
-      <c r="D9" s="19" t="s">
-        <v>30</v>
-      </c>
+      <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="I9" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="J9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="N9" s="19"/>
+      <c r="O9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="R9" s="19"/>
+      <c r="S9" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="P9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="S9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="T9" s="23"/>
+      <c r="T9" s="19" t="s">
+        <v>25</v>
+      </c>
       <c r="U9" s="23"/>
       <c r="V9" s="23"/>
       <c r="W9" s="23"/>
@@ -3433,8 +3503,9 @@
       <c r="AJ9" s="23"/>
       <c r="AK9" s="23"/>
       <c r="AL9" s="23"/>
-    </row>
-    <row r="10" spans="1:38">
+      <c r="AM9" s="23"/>
+    </row>
+    <row r="10" spans="1:39" ht="238">
       <c r="A10" s="24">
         <v>46085</v>
       </c>
@@ -3442,101 +3513,103 @@
         <v>46078</v>
       </c>
       <c r="C10" s="24"/>
-      <c r="D10" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="D10" s="24"/>
       <c r="E10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="I10" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="J10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="L10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="5" t="s">
+      <c r="N10" s="26">
+        <v>46071</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P10" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="5" t="s">
+      <c r="Q10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="M10" s="26">
-        <v>46071</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:38" ht="15.75" customHeight="1">
+      <c r="T10" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" ht="15.75" customHeight="1">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="I11" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="15" t="s">
+      <c r="J11" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="K11" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="L11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="P11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:38">
+      <c r="T11" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" ht="62.5">
       <c r="A12" s="17">
         <v>46085</v>
       </c>
@@ -3544,99 +3617,101 @@
         <v>46077</v>
       </c>
       <c r="C12" s="17"/>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="17"/>
+      <c r="E12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="H12" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="I12" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="J12" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="K12" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="L12" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="J12" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="K12" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="M12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" s="5"/>
       <c r="O12" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5" t="s">
-        <v>90</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R12" s="5"/>
       <c r="S12" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:38" ht="15.75" customHeight="1">
+        <v>88</v>
+      </c>
+      <c r="T12" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" ht="15.75" customHeight="1">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
-      <c r="D13" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H13" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="J13" s="5"/>
+      <c r="K13" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="L13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="9" t="s">
+      <c r="N13" s="5"/>
+      <c r="O13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L13" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="S13" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:38">
+      <c r="T13" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39" ht="50">
       <c r="A14" s="17">
         <v>46085</v>
       </c>
@@ -3644,52 +3719,53 @@
         <v>46077</v>
       </c>
       <c r="C14" s="17"/>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="17"/>
+      <c r="E14" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="H14" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="I14" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="J14" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="K14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="I14" s="27" t="s">
+      <c r="N14" s="5"/>
+      <c r="O14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P14" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="J14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L14" s="9" t="s">
+      <c r="Q14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="S14" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:38">
+      <c r="T14" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39" ht="113">
       <c r="A15" s="17">
         <v>46085</v>
       </c>
@@ -3697,99 +3773,101 @@
         <v>46077</v>
       </c>
       <c r="C15" s="17"/>
-      <c r="D15" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="D15" s="17"/>
       <c r="E15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H15" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="I15" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="J15" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="K15" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="I15" s="27" t="s">
+      <c r="L15" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="J15" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="M15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N15" s="5"/>
       <c r="O15" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R15" s="5"/>
       <c r="S15" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:38">
+        <v>25</v>
+      </c>
+      <c r="T15" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" ht="42">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
-      <c r="D16" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="I16" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="J16" s="5"/>
+      <c r="K16" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="L16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="5"/>
+      <c r="N16" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="27" t="s">
+      <c r="O16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P16" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="K16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" s="5"/>
-      <c r="M16" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="P16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5" t="s">
-        <v>114</v>
-      </c>
+      <c r="Q16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R16" s="5"/>
       <c r="S16" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19">
+        <v>112</v>
+      </c>
+      <c r="T16" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="50.5">
       <c r="A17" s="17">
         <v>46085</v>
       </c>
@@ -3797,144 +3875,147 @@
         <v>46077</v>
       </c>
       <c r="C17" s="17"/>
-      <c r="D17" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="D17" s="17"/>
       <c r="E17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="I17" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="J17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="M17" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" s="5" t="s">
+      <c r="N17" s="5"/>
+      <c r="O17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R17" s="5"/>
+      <c r="S17" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="L17" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="S17" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19">
+      <c r="T17" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="100.5">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="5"/>
+      <c r="E18" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="H18" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="I18" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="G18" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="I18" s="28"/>
-      <c r="J18" s="5"/>
+      <c r="J18" s="28"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
-      <c r="M18" s="5" t="s">
+      <c r="M18" s="5"/>
+      <c r="N18" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q18" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5" t="s">
+      <c r="R18" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="P18" s="28" t="s">
+      <c r="S18" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="Q18" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="R18" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="S18" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" customHeight="1">
+      <c r="T18" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15.75" customHeight="1">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="5" t="s">
-        <v>106</v>
-      </c>
+      <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="H19" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="I19" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="J19" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="K19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="M19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="J19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="S19" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19">
+      <c r="T19" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="39">
       <c r="A20" s="17">
         <v>46087</v>
       </c>
@@ -3942,201 +4023,205 @@
         <v>46077</v>
       </c>
       <c r="C20" s="17"/>
-      <c r="D20" s="5" t="s">
-        <v>106</v>
-      </c>
+      <c r="D20" s="17"/>
       <c r="E20" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="H20" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="I20" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="J20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="H20" s="29" t="s">
+      <c r="L20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="I20" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="N20" s="5"/>
       <c r="O20" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R20" s="5"/>
       <c r="S20" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="15.75" customHeight="1">
+        <v>25</v>
+      </c>
+      <c r="T20" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="15.75" customHeight="1">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="5" t="s">
-        <v>136</v>
-      </c>
+      <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H21" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="I21" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="J21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="M21" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="H21" s="14" t="s">
+      <c r="N21" s="5"/>
+      <c r="O21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="T21" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="50.5">
+      <c r="A22" s="30" t="s">
         <v>162</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="S21" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="50.5">
-      <c r="A22" s="30" t="s">
-        <v>164</v>
       </c>
       <c r="B22" s="31">
         <v>46077</v>
       </c>
       <c r="C22" s="31"/>
-      <c r="D22" s="5" t="s">
-        <v>83</v>
-      </c>
+      <c r="D22" s="31"/>
       <c r="E22" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H22" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="I22" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="G22" s="32" t="s">
+      <c r="J22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="M22" s="5"/>
+      <c r="N22" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="I22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K22" s="5" t="s">
+      <c r="O22" s="5"/>
+      <c r="P22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="L22" s="5"/>
-      <c r="M22" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="S22" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="37.5">
+      <c r="T22" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="37.5">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="5" t="s">
-        <v>83</v>
-      </c>
+      <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H23" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="I23" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="J23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="L23" s="5"/>
+      <c r="M23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N23" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J23" s="5" t="s">
+      <c r="O23" s="5"/>
+      <c r="P23" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R23" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M23" s="5" t="s">
+      <c r="S23" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="N23" s="5"/>
-      <c r="O23" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q23" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="R23" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="S23" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="37.5">
+      <c r="T23" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="37.5">
       <c r="A24" s="33">
         <v>46086</v>
       </c>
@@ -4144,52 +4229,53 @@
         <v>46078</v>
       </c>
       <c r="C24" s="33"/>
-      <c r="D24" s="5" t="s">
-        <v>136</v>
-      </c>
+      <c r="D24" s="33"/>
       <c r="E24" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="H24" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="I24" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="J24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K24" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="L24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J24" s="8" t="s">
+      <c r="N24" s="5"/>
+      <c r="O24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R24" s="5"/>
+      <c r="S24" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="K24" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O24" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P24" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="S24" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="51">
+      <c r="T24" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="51">
       <c r="A25" s="17">
         <v>46085</v>
       </c>
@@ -4197,50 +4283,51 @@
         <v>46077</v>
       </c>
       <c r="C25" s="17"/>
-      <c r="D25" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="D25" s="17"/>
       <c r="E25" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="H25" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="I25" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="J25" s="5"/>
+      <c r="K25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="N25" s="8"/>
+      <c r="O25" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="O25" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="P25" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R25" s="5"/>
       <c r="S25" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="63">
+        <v>25</v>
+      </c>
+      <c r="T25" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="63">
       <c r="A26" s="17">
         <v>46085</v>
       </c>
@@ -4248,54 +4335,55 @@
         <v>46077</v>
       </c>
       <c r="C26" s="17"/>
-      <c r="D26" s="5" t="s">
-        <v>106</v>
-      </c>
+      <c r="D26" s="17"/>
       <c r="E26" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H26" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="I26" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="J26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N26" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="H26" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="N26" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="O26" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R26" s="5"/>
       <c r="S26" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="116">
+        <v>25</v>
+      </c>
+      <c r="T26" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="116">
       <c r="A27" s="17">
         <v>46085</v>
       </c>
@@ -4303,104 +4391,107 @@
         <v>46077</v>
       </c>
       <c r="C27" s="17"/>
-      <c r="D27" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="D27" s="17"/>
       <c r="E27" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="H27" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="I27" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="J27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N27" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="O27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P27" s="35" t="s">
         <v>201</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M27" s="35" t="s">
+      <c r="Q27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="N27" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O27" s="35" t="s">
-        <v>203</v>
-      </c>
-      <c r="P27" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="S27" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="63">
+      <c r="T27" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="63">
+      <c r="A28" s="28"/>
       <c r="B28" s="17">
         <v>46085</v>
       </c>
       <c r="C28" s="17"/>
-      <c r="D28" s="5" t="s">
-        <v>106</v>
-      </c>
+      <c r="D28" s="17"/>
       <c r="E28" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H28" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="I28" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="J28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="P28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="I28" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="O28" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P28" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="S28" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="25.5">
+      <c r="T28" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="25.5">
       <c r="A29" s="17">
         <v>46085</v>
       </c>
@@ -4408,103 +4499,105 @@
         <v>46077</v>
       </c>
       <c r="C29" s="17"/>
-      <c r="D29" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="D29" s="17"/>
       <c r="E29" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="H29" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="I29" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="J29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K29" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H29" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="L29" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N29" s="5"/>
       <c r="O29" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R29" s="5"/>
       <c r="S29" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="42">
+        <v>25</v>
+      </c>
+      <c r="T29" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="42">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="5"/>
+      <c r="E30" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="G30" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="H30" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="I30" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="J30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N30" s="36" t="s">
         <v>219</v>
       </c>
-      <c r="H30" s="16" t="s">
+      <c r="O30" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M30" s="36" t="s">
+      <c r="P30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="N30" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="O30" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P30" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="S30" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="125.5">
+      <c r="T30" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="125.5">
       <c r="A31" s="17">
         <v>46085</v>
       </c>
@@ -4512,52 +4605,53 @@
         <v>46077</v>
       </c>
       <c r="C31" s="17"/>
-      <c r="D31" s="5" t="s">
-        <v>216</v>
-      </c>
+      <c r="D31" s="17"/>
       <c r="E31" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H31" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="I31" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="G31" s="15" t="s">
+      <c r="J31" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="H31" s="16" t="s">
+      <c r="L31" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M31" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J31" s="8" t="s">
+      <c r="N31" s="5"/>
+      <c r="O31" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P31" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="K31" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L31" s="9" t="s">
+      <c r="Q31" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O31" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="P31" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="S31" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="50">
+      <c r="T31" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="50">
       <c r="A32" s="17">
         <v>46085</v>
       </c>
@@ -4565,52 +4659,53 @@
         <v>46077</v>
       </c>
       <c r="C32" s="17"/>
-      <c r="D32" s="5" t="s">
-        <v>136</v>
-      </c>
+      <c r="D32" s="17"/>
       <c r="E32" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H32" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="I32" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="J32" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="H32" s="25" t="s">
+      <c r="K32" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="N32" s="9"/>
+      <c r="O32" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="J32" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="O32" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="P32" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5" t="s">
-        <v>105</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R32" s="5"/>
       <c r="S32" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="50.5">
+        <v>103</v>
+      </c>
+      <c r="T32" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="50.5">
       <c r="A33" s="17">
         <v>46085</v>
       </c>
@@ -4618,148 +4713,151 @@
         <v>46077</v>
       </c>
       <c r="C33" s="17"/>
-      <c r="D33" s="5" t="s">
-        <v>106</v>
-      </c>
+      <c r="D33" s="17"/>
       <c r="E33" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="H33" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="I33" s="37" t="s">
         <v>240</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="J33" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="K33" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="H33" s="37" t="s">
+      <c r="L33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M33" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="I33" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="N33" s="5"/>
       <c r="O33" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5" t="s">
-        <v>105</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R33" s="5"/>
       <c r="S33" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="37.5">
+        <v>103</v>
+      </c>
+      <c r="T33" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="37.5">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="5" t="s">
-        <v>136</v>
-      </c>
+      <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H34" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="I34" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="G34" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L34" s="38">
-        <v>46030</v>
+        <v>25</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="M34" s="38">
         <v>46030</v>
       </c>
-      <c r="N34" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O34" s="28"/>
-      <c r="P34" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q34" s="5"/>
-      <c r="R34" s="5" t="s">
-        <v>105</v>
-      </c>
+      <c r="N34" s="38">
+        <v>46030</v>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R34" s="5"/>
       <c r="S34" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="63">
+        <v>103</v>
+      </c>
+      <c r="T34" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="63">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
-      <c r="D35" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="39" t="s">
+      <c r="D35" s="5"/>
+      <c r="E35" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="39" t="s">
+        <v>247</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="H35" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="I35" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="G35" s="15" t="s">
+      <c r="J35" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="H35" s="40" t="s">
+      <c r="K35" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="P35" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="J35" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K35" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="L35" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="O35" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="P35" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q35" s="5"/>
-      <c r="R35" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="Q35" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R35" s="5"/>
       <c r="S35" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="38">
+        <v>25</v>
+      </c>
+      <c r="T35" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="38">
       <c r="A36" s="17">
         <v>46085</v>
       </c>
@@ -4767,52 +4865,53 @@
         <v>46077</v>
       </c>
       <c r="C36" s="17"/>
-      <c r="D36" s="5" t="s">
-        <v>216</v>
-      </c>
+      <c r="D36" s="17"/>
       <c r="E36" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="H36" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="I36" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="G36" s="15" t="s">
+      <c r="J36" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="H36" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L36" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="N36" s="5"/>
       <c r="O36" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R36" s="5"/>
       <c r="S36" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="100.5">
+        <v>25</v>
+      </c>
+      <c r="T36" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="100.5">
       <c r="A37" s="17">
         <v>46085</v>
       </c>
@@ -4820,99 +4919,101 @@
         <v>46077</v>
       </c>
       <c r="C37" s="17"/>
-      <c r="D37" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="D37" s="17"/>
       <c r="E37" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="H37" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="I37" s="87" t="s">
         <v>262</v>
       </c>
-      <c r="G37" s="15" t="s">
+      <c r="J37" s="88"/>
+      <c r="K37" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L37" s="28"/>
+      <c r="M37" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="H37" s="92" t="s">
+      <c r="N37" s="9"/>
+      <c r="O37" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="I37" s="93"/>
-      <c r="J37" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K37" s="28"/>
-      <c r="L37" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="M37" s="9"/>
-      <c r="N37" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="O37" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="P37" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q37" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R37" s="5"/>
       <c r="S37" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" ht="50">
+        <v>25</v>
+      </c>
+      <c r="T37" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="50">
       <c r="A38" s="17">
         <v>46085</v>
       </c>
       <c r="B38" s="42" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C38" s="42"/>
-      <c r="D38" s="5" t="s">
-        <v>106</v>
-      </c>
+      <c r="D38" s="42"/>
       <c r="E38" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="H38" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="I38" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="G38" s="15" t="s">
+      <c r="J38" s="5"/>
+      <c r="K38" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M38" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="H38" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L38" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="N38" s="5"/>
       <c r="O38" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q38" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R38" s="5"/>
       <c r="S38" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="50.5">
+        <v>25</v>
+      </c>
+      <c r="T38" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="50.5">
       <c r="A39" s="17">
         <v>46085</v>
       </c>
@@ -4920,52 +5021,53 @@
         <v>46077</v>
       </c>
       <c r="C39" s="17"/>
-      <c r="D39" s="5" t="s">
-        <v>216</v>
-      </c>
+      <c r="D39" s="17"/>
       <c r="E39" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="H39" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="I39" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="G39" s="15" t="s">
+      <c r="J39" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="K39" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M39" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="I39" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L39" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="N39" s="5"/>
       <c r="O39" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P39" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q39" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R39" s="5"/>
       <c r="S39" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="50.5">
+        <v>25</v>
+      </c>
+      <c r="T39" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="50.5">
       <c r="A40" s="17">
         <v>46085</v>
       </c>
@@ -4973,52 +5075,53 @@
         <v>46077</v>
       </c>
       <c r="C40" s="17"/>
-      <c r="D40" s="5" t="s">
-        <v>216</v>
-      </c>
+      <c r="D40" s="17"/>
       <c r="E40" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="H40" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="I40" s="43" t="s">
         <v>279</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="J40" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="H40" s="43" t="s">
+      <c r="K40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R40" s="5"/>
+      <c r="S40" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="I40" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L40" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O40" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P40" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="S40" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" ht="88">
+      <c r="T40" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="88">
       <c r="A41" s="17">
         <v>46085</v>
       </c>
@@ -5026,52 +5129,53 @@
         <v>46077</v>
       </c>
       <c r="C41" s="17"/>
-      <c r="D41" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="D41" s="17"/>
       <c r="E41" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="H41" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="I41" s="16" t="s">
         <v>285</v>
       </c>
-      <c r="G41" s="15" t="s">
+      <c r="J41" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="H41" s="16" t="s">
+      <c r="K41" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L41" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="I41" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K41" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="L41" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="M41" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N41" s="5"/>
       <c r="O41" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q41" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R41" s="5"/>
       <c r="S41" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" ht="50.5">
+        <v>25</v>
+      </c>
+      <c r="T41" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" ht="50.5">
       <c r="A42" s="17">
         <v>46085</v>
       </c>
@@ -5079,52 +5183,53 @@
         <v>46077</v>
       </c>
       <c r="C42" s="17"/>
-      <c r="D42" s="5" t="s">
-        <v>136</v>
-      </c>
+      <c r="D42" s="17"/>
       <c r="E42" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="H42" s="44" t="s">
         <v>290</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="I42" s="45" t="s">
         <v>291</v>
       </c>
-      <c r="G42" s="44" t="s">
+      <c r="J42" s="25" t="s">
         <v>292</v>
       </c>
-      <c r="H42" s="45" t="s">
+      <c r="K42" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="I42" s="25" t="s">
+      <c r="L42" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M42" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P42" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q42" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R42" s="5"/>
+      <c r="S42" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="J42" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="S42" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="28">
+      <c r="T42" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="28">
       <c r="A43" s="31">
         <v>46085</v>
       </c>
@@ -5132,52 +5237,53 @@
         <v>46077</v>
       </c>
       <c r="C43" s="31"/>
-      <c r="D43" s="5" t="s">
-        <v>136</v>
-      </c>
+      <c r="D43" s="31"/>
       <c r="E43" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="H43" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="I43" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="G43" s="15" t="s">
+      <c r="J43" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M43" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="H43" s="16" t="s">
+      <c r="N43" s="5"/>
+      <c r="O43" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P43" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L43" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="P43" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="Q43" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R43" s="5"/>
       <c r="S43" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="76">
+        <v>25</v>
+      </c>
+      <c r="T43" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="76">
       <c r="A44" s="17">
         <v>46085</v>
       </c>
@@ -5185,101 +5291,103 @@
         <v>46077</v>
       </c>
       <c r="C44" s="17"/>
-      <c r="D44" s="5" t="s">
-        <v>106</v>
-      </c>
+      <c r="D44" s="17"/>
       <c r="E44" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="H44" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="I44" s="46" t="s">
         <v>304</v>
       </c>
-      <c r="G44" s="12" t="s">
+      <c r="J44" s="25" t="s">
         <v>305</v>
       </c>
-      <c r="H44" s="46" t="s">
+      <c r="K44" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L44" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="I44" s="25" t="s">
-        <v>307</v>
-      </c>
-      <c r="J44" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K44" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="L44" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="M44" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N44" s="5"/>
       <c r="O44" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P44" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q44" s="5"/>
-      <c r="R44" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q44" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R44" s="5"/>
       <c r="S44" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" ht="50">
+        <v>25</v>
+      </c>
+      <c r="T44" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" ht="50">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="5" t="s">
-        <v>136</v>
-      </c>
+      <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="H45" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="I45" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="G45" s="15" t="s">
+      <c r="J45" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="H45" s="8" t="s">
+      <c r="K45" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="I45" s="5" t="s">
+      <c r="L45" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M45" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="J45" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="K45" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L45" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="N45" s="5"/>
       <c r="O45" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P45" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q45" s="5"/>
-      <c r="R45" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q45" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R45" s="5"/>
       <c r="S45" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="125.5">
+        <v>25</v>
+      </c>
+      <c r="T45" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="125.5">
       <c r="A46" s="17">
         <v>46085</v>
       </c>
@@ -5287,52 +5395,53 @@
         <v>46077</v>
       </c>
       <c r="C46" s="17"/>
-      <c r="D46" s="5" t="s">
-        <v>106</v>
-      </c>
+      <c r="D46" s="17"/>
       <c r="E46" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H46" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="I46" s="47" t="s">
         <v>317</v>
       </c>
-      <c r="G46" s="15" t="s">
+      <c r="J46" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K46" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="H46" s="47" t="s">
-        <v>319</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="K46" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="L46" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M46" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N46" s="5"/>
       <c r="O46" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P46" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q46" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R46" s="5"/>
       <c r="S46" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="50">
+        <v>25</v>
+      </c>
+      <c r="T46" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" ht="50">
       <c r="A47" s="17">
         <v>46085</v>
       </c>
@@ -5340,52 +5449,53 @@
         <v>46077</v>
       </c>
       <c r="C47" s="17"/>
-      <c r="D47" s="5" t="s">
-        <v>216</v>
-      </c>
+      <c r="D47" s="17"/>
       <c r="E47" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="H47" s="48" t="s">
         <v>321</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="I47" s="16" t="s">
         <v>322</v>
       </c>
-      <c r="G47" s="48" t="s">
+      <c r="J47" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="H47" s="16" t="s">
+      <c r="K47" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M47" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="I47" s="8" t="s">
+      <c r="N47" s="5"/>
+      <c r="O47" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="J47" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K47" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L47" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="M47" s="5"/>
-      <c r="N47" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="O47" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="P47" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q47" s="5"/>
-      <c r="R47" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q47" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R47" s="5"/>
       <c r="S47" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="50">
+        <v>25</v>
+      </c>
+      <c r="T47" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="50">
       <c r="A48" s="17">
         <v>46085</v>
       </c>
@@ -5393,35 +5503,37 @@
         <v>46077</v>
       </c>
       <c r="C48" s="17"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="49" t="s">
+      <c r="D48" s="17"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="49" t="s">
+        <v>326</v>
+      </c>
+      <c r="G48" s="27" t="s">
+        <v>327</v>
+      </c>
+      <c r="H48" s="50" t="s">
         <v>328</v>
       </c>
-      <c r="F48" s="27" t="s">
+      <c r="I48" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="G48" s="50" t="s">
+      <c r="J48" s="28"/>
+      <c r="K48" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="L48" s="49" t="s">
         <v>330</v>
       </c>
-      <c r="H48" s="51" t="s">
-        <v>331</v>
-      </c>
-      <c r="J48" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="K48" s="49" t="s">
-        <v>332</v>
-      </c>
-      <c r="L48" s="8"/>
-      <c r="M48" s="5"/>
+      <c r="M48" s="8"/>
       <c r="N48" s="5"/>
       <c r="O48" s="5"/>
       <c r="P48" s="5"/>
       <c r="Q48" s="5"/>
       <c r="R48" s="5"/>
       <c r="S48" s="5"/>
-    </row>
-    <row r="49" spans="1:38" ht="50">
+      <c r="T48" s="5"/>
+    </row>
+    <row r="49" spans="1:39" ht="50">
       <c r="A49" s="17">
         <v>46085</v>
       </c>
@@ -5429,38 +5541,39 @@
         <v>46077</v>
       </c>
       <c r="C49" s="17"/>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="17"/>
+      <c r="E49" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G49" s="28" t="s">
         <v>333</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="H49" s="32" t="s">
         <v>334</v>
       </c>
-      <c r="F49" s="52" t="s">
+      <c r="I49" s="49" t="s">
         <v>335</v>
       </c>
-      <c r="G49" s="53" t="s">
+      <c r="J49" s="49" t="s">
         <v>336</v>
       </c>
-      <c r="H49" s="49" t="s">
+      <c r="K49" s="49" t="s">
         <v>337</v>
       </c>
-      <c r="I49" s="49" t="s">
-        <v>338</v>
-      </c>
-      <c r="J49" s="49" t="s">
-        <v>339</v>
-      </c>
-      <c r="K49" s="5"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="8"/>
       <c r="N49" s="5"/>
       <c r="O49" s="5"/>
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
       <c r="R49" s="5"/>
       <c r="S49" s="5"/>
-    </row>
-    <row r="50" spans="1:38" ht="62.5">
+      <c r="T49" s="5"/>
+    </row>
+    <row r="50" spans="1:39" ht="62.5">
       <c r="A50" s="17">
         <v>46085</v>
       </c>
@@ -5468,83 +5581,85 @@
         <v>46077</v>
       </c>
       <c r="C50" s="17"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="12" t="s">
+      <c r="D50" s="17"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="G50" s="28" t="s">
+        <v>339</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="I50" s="49" t="s">
+        <v>310</v>
+      </c>
+      <c r="J50" s="49" t="s">
         <v>340</v>
       </c>
-      <c r="F50" s="52" t="s">
-        <v>341</v>
-      </c>
-      <c r="G50" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="H50" s="49" t="s">
-        <v>312</v>
-      </c>
-      <c r="I50" s="49" t="s">
-        <v>342</v>
-      </c>
-      <c r="J50" s="49"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="8"/>
-      <c r="M50" s="5"/>
+      <c r="K50" s="49"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="8"/>
       <c r="N50" s="5"/>
       <c r="O50" s="5"/>
       <c r="P50" s="5"/>
       <c r="Q50" s="5"/>
       <c r="R50" s="5"/>
       <c r="S50" s="5"/>
-    </row>
-    <row r="51" spans="1:38" ht="42">
+      <c r="T50" s="5"/>
+    </row>
+    <row r="51" spans="1:39" ht="42">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="5" t="s">
-        <v>216</v>
-      </c>
+      <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="H51" s="44" t="s">
         <v>343</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="I51" s="40" t="s">
         <v>344</v>
       </c>
-      <c r="G51" s="44" t="s">
+      <c r="J51" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="H51" s="40" t="s">
-        <v>346</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="J51" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="K51" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L51" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N51" s="5"/>
       <c r="O51" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P51" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q51" s="5"/>
-      <c r="R51" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q51" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R51" s="5"/>
       <c r="S51" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:38" ht="38">
+        <v>25</v>
+      </c>
+      <c r="T51" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:39" ht="38">
       <c r="A52" s="17">
         <v>46086</v>
       </c>
@@ -5552,443 +5667,452 @@
         <v>46077</v>
       </c>
       <c r="C52" s="17"/>
-      <c r="D52" s="5" t="s">
-        <v>136</v>
-      </c>
+      <c r="D52" s="17"/>
       <c r="E52" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="H52" s="15" t="s">
         <v>348</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="I52" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="G52" s="15" t="s">
+      <c r="J52" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="H52" s="5" t="s">
+      <c r="K52" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L52" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P52" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q52" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R52" s="5"/>
+      <c r="S52" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="T52" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:39" ht="75">
+      <c r="A53" s="5" t="s">
         <v>351</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="J52" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K52" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L52" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O52" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P52" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q52" s="5"/>
-      <c r="R52" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="S52" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:38" ht="75">
-      <c r="A53" s="5" t="s">
-        <v>353</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="5" t="s">
-        <v>106</v>
-      </c>
+      <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H53" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="I53" s="51" t="s">
         <v>355</v>
       </c>
-      <c r="G53" s="15" t="s">
+      <c r="J53" s="51" t="s">
         <v>356</v>
       </c>
-      <c r="H53" s="54" t="s">
-        <v>357</v>
-      </c>
-      <c r="I53" s="54" t="s">
-        <v>358</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="K53" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L53" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M53" s="5"/>
-      <c r="N53" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N53" s="5"/>
       <c r="O53" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P53" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q53" s="5"/>
-      <c r="R53" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q53" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R53" s="5"/>
       <c r="S53" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:38" ht="150">
+        <v>25</v>
+      </c>
+      <c r="T53" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:39" ht="150">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H54" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="I54" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="G54" s="15" t="s">
+      <c r="J54" s="51" t="s">
         <v>361</v>
       </c>
-      <c r="H54" s="5" t="s">
+      <c r="K54" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="I54" s="54" t="s">
+      <c r="L54" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="M54" s="51" t="s">
         <v>363</v>
       </c>
-      <c r="J54" s="5" t="s">
+      <c r="N54" s="5"/>
+      <c r="O54" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P54" s="28" t="s">
         <v>364</v>
       </c>
-      <c r="K54" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="L54" s="54" t="s">
-        <v>365</v>
-      </c>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O54" s="28" t="s">
-        <v>366</v>
-      </c>
-      <c r="P54" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q54" s="5"/>
-      <c r="R54" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="Q54" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R54" s="5"/>
       <c r="S54" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:38" ht="37.5">
+        <v>25</v>
+      </c>
+      <c r="T54" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:39" ht="37.5">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="5" t="s">
-        <v>216</v>
-      </c>
+      <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="H55" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="I55" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="G55" s="15" t="s">
+      <c r="J55" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="H55" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="K55" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L55" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M55" s="5"/>
-      <c r="N55" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N55" s="5"/>
       <c r="O55" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P55" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q55" s="5"/>
-      <c r="R55" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q55" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R55" s="5"/>
       <c r="S55" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56" spans="1:38" ht="42">
+        <v>25</v>
+      </c>
+      <c r="T55" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:39" ht="42">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="H56" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="I56" s="37" t="s">
         <v>373</v>
       </c>
-      <c r="G56" s="15" t="s">
+      <c r="J56" s="5"/>
+      <c r="K56" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L56" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M56" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="H56" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K56" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L56" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="M56" s="5"/>
-      <c r="N56" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="N56" s="5"/>
       <c r="O56" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P56" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q56" s="5"/>
-      <c r="R56" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q56" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R56" s="5"/>
       <c r="S56" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:38" ht="70">
+        <v>25</v>
+      </c>
+      <c r="T56" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:39" ht="70">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="5" t="s">
-        <v>136</v>
-      </c>
+      <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="H57" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="I57" s="37" t="s">
         <v>378</v>
       </c>
-      <c r="G57" s="12" t="s">
+      <c r="J57" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="H57" s="37" t="s">
+      <c r="K57" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L57" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M57" s="25" t="s">
         <v>380</v>
       </c>
-      <c r="I57" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="J57" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K57" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L57" s="25" t="s">
-        <v>382</v>
-      </c>
-      <c r="M57" s="5"/>
-      <c r="N57" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="N57" s="5"/>
       <c r="O57" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P57" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q57" s="5"/>
-      <c r="R57" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q57" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R57" s="5"/>
       <c r="S57" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="58" spans="1:38" ht="50">
+        <v>25</v>
+      </c>
+      <c r="T57" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:39" ht="50">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="H58" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="I58" s="52" t="s">
         <v>384</v>
       </c>
-      <c r="G58" s="15" t="s">
-        <v>385</v>
-      </c>
-      <c r="H58" s="55" t="s">
-        <v>386</v>
-      </c>
-      <c r="I58" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="J58" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="K58" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="L58" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="M58" s="55"/>
-      <c r="N58" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="O58" s="5" t="s">
-        <v>27</v>
+      <c r="J58" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="K58" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="L58" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="M58" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="N58" s="52"/>
+      <c r="O58" s="52" t="s">
+        <v>25</v>
       </c>
       <c r="P58" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q58" s="5"/>
-      <c r="R58" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="S58" s="55" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:38" ht="37.5">
+        <v>25</v>
+      </c>
+      <c r="Q58" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R58" s="5"/>
+      <c r="S58" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="T58" s="52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:39" ht="37.5">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="5" t="s">
-        <v>216</v>
-      </c>
+      <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="G59" s="5"/>
+      <c r="H59" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="I59" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="F59" s="5"/>
-      <c r="G59" s="15" t="s">
+      <c r="J59" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="H59" s="16" t="s">
-        <v>389</v>
-      </c>
-      <c r="I59" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="J59" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="K59" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="L59" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="M59" s="55"/>
-      <c r="N59" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="O59" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="P59" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q59" s="55"/>
-      <c r="R59" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="S59" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="AL59" s="56"/>
-    </row>
-    <row r="60" spans="1:38" ht="28">
+      <c r="K59" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="L59" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="M59" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="N59" s="52"/>
+      <c r="O59" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="P59" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q59" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="R59" s="52"/>
+      <c r="S59" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="T59" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM59" s="53"/>
+    </row>
+    <row r="60" spans="1:39" ht="28">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="5" t="s">
-        <v>216</v>
-      </c>
+      <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="H60" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="I60" s="37" t="s">
         <v>392</v>
       </c>
-      <c r="G60" s="12" t="s">
+      <c r="J60" s="37" t="s">
         <v>393</v>
       </c>
-      <c r="H60" s="37" t="s">
-        <v>394</v>
-      </c>
-      <c r="I60" s="37" t="s">
-        <v>395</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="K60" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L60" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M60" s="5"/>
-      <c r="N60" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M60" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N60" s="5"/>
       <c r="O60" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P60" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q60" s="5"/>
-      <c r="R60" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q60" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R60" s="5"/>
       <c r="S60" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:38" ht="25.5">
+        <v>25</v>
+      </c>
+      <c r="T60" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:39" ht="25.5">
       <c r="A61" s="17">
         <v>46086</v>
       </c>
@@ -5996,51 +6120,53 @@
         <v>46080</v>
       </c>
       <c r="C61" s="17"/>
-      <c r="D61" s="5" t="s">
-        <v>136</v>
-      </c>
+      <c r="D61" s="17"/>
       <c r="E61" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="H61" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="I61" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="G61" s="15" t="s">
+      <c r="J61" s="28"/>
+      <c r="K61" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L61" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N61" s="54" t="s">
         <v>398</v>
       </c>
-      <c r="H61" s="5" t="s">
+      <c r="O61" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P61" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="J61" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K61" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L61" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M61" s="95" t="s">
-        <v>562</v>
-      </c>
-      <c r="N61" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O61" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="P61" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q61" s="5"/>
-      <c r="R61" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="Q61" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R61" s="5"/>
       <c r="S61" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:38" ht="50.5">
+        <v>25</v>
+      </c>
+      <c r="T61" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:39" ht="50.5">
       <c r="A62" s="17">
         <v>46085</v>
       </c>
@@ -6048,176 +6174,180 @@
         <v>46077</v>
       </c>
       <c r="C62" s="17"/>
-      <c r="D62" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E62" s="58" t="s">
+      <c r="D62" s="17"/>
+      <c r="E62" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="56" t="s">
+        <v>400</v>
+      </c>
+      <c r="G62" s="55" t="s">
         <v>401</v>
       </c>
-      <c r="F62" s="57" t="s">
+      <c r="H62" s="57" t="s">
         <v>402</v>
       </c>
-      <c r="G62" s="59" t="s">
+      <c r="I62" s="58" t="s">
         <v>403</v>
       </c>
-      <c r="H62" s="60" t="s">
+      <c r="J62" s="55" t="s">
         <v>404</v>
       </c>
-      <c r="I62" s="57" t="s">
-        <v>405</v>
-      </c>
-      <c r="J62" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="K62" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="L62" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="M62" s="57"/>
-      <c r="N62" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="O62" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="P62" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q62" s="57"/>
-      <c r="R62" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="S62" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="T62" s="61"/>
-      <c r="U62" s="61"/>
-      <c r="V62" s="61"/>
-      <c r="W62" s="61"/>
-      <c r="X62" s="61"/>
-      <c r="Y62" s="61"/>
-      <c r="Z62" s="61"/>
-      <c r="AA62" s="61"/>
-      <c r="AB62" s="61"/>
-      <c r="AC62" s="61"/>
-      <c r="AD62" s="61"/>
-      <c r="AE62" s="61"/>
-      <c r="AF62" s="61"/>
-      <c r="AG62" s="61"/>
-      <c r="AH62" s="61"/>
-      <c r="AI62" s="61"/>
-      <c r="AJ62" s="61"/>
-      <c r="AK62" s="61"/>
-      <c r="AL62" s="61"/>
-    </row>
-    <row r="63" spans="1:38" ht="75.5">
+      <c r="K62" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="L62" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="M62" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="N62" s="55"/>
+      <c r="O62" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="P62" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q62" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="R62" s="55"/>
+      <c r="S62" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="T62" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="U62" s="59"/>
+      <c r="V62" s="59"/>
+      <c r="W62" s="59"/>
+      <c r="X62" s="59"/>
+      <c r="Y62" s="59"/>
+      <c r="Z62" s="59"/>
+      <c r="AA62" s="59"/>
+      <c r="AB62" s="59"/>
+      <c r="AC62" s="59"/>
+      <c r="AD62" s="59"/>
+      <c r="AE62" s="59"/>
+      <c r="AF62" s="59"/>
+      <c r="AG62" s="59"/>
+      <c r="AH62" s="59"/>
+      <c r="AI62" s="59"/>
+      <c r="AJ62" s="59"/>
+      <c r="AK62" s="59"/>
+      <c r="AL62" s="59"/>
+      <c r="AM62" s="59"/>
+    </row>
+    <row r="63" spans="1:39" ht="75.5">
+      <c r="A63" s="28"/>
       <c r="B63" s="17">
         <v>46085</v>
       </c>
-      <c r="C63" s="42">
+      <c r="C63" s="17"/>
+      <c r="D63" s="42">
         <v>3</v>
       </c>
-      <c r="D63" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="E63" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="G63" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="H63" s="15" t="s">
         <v>407</v>
       </c>
-      <c r="G63" s="15" t="s">
+      <c r="I63" s="16" t="s">
         <v>408</v>
       </c>
-      <c r="H63" s="16" t="s">
+      <c r="J63" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="I63" s="5" t="s">
+      <c r="K63" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="J63" s="5" t="s">
+      <c r="L63" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M63" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="K63" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L63" s="5" t="s">
+      <c r="N63" s="5"/>
+      <c r="O63" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P63" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="M63" s="5"/>
-      <c r="N63" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O63" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="P63" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q63" s="5"/>
-      <c r="R63" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="Q63" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R63" s="5"/>
       <c r="S63" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="64" spans="1:38" ht="50.5">
+        <v>25</v>
+      </c>
+      <c r="T63" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:39" ht="50.5">
       <c r="A64" s="17"/>
       <c r="B64" s="17">
         <v>46085</v>
       </c>
-      <c r="C64" s="42">
+      <c r="C64" s="17"/>
+      <c r="D64" s="42">
         <v>3</v>
       </c>
-      <c r="D64" s="5" t="s">
-        <v>106</v>
-      </c>
       <c r="E64" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="G64" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="H64" s="15" t="s">
         <v>415</v>
       </c>
-      <c r="G64" s="15" t="s">
+      <c r="I64" s="37" t="s">
         <v>416</v>
       </c>
-      <c r="H64" s="37" t="s">
+      <c r="J64" s="37" t="s">
         <v>417</v>
       </c>
-      <c r="I64" s="37" t="s">
-        <v>418</v>
-      </c>
-      <c r="J64" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="K64" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L64" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M64" s="5"/>
-      <c r="N64" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M64" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N64" s="5"/>
       <c r="O64" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P64" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q64" s="5"/>
-      <c r="R64" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q64" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R64" s="5"/>
       <c r="S64" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="65" spans="1:38" ht="28">
+        <v>25</v>
+      </c>
+      <c r="T64" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:39" ht="28">
       <c r="A65" s="17">
         <v>46085</v>
       </c>
@@ -6225,52 +6355,53 @@
         <v>46077</v>
       </c>
       <c r="C65" s="17"/>
-      <c r="D65" s="5" t="s">
-        <v>136</v>
-      </c>
+      <c r="D65" s="17"/>
       <c r="E65" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="G65" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="H65" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="G65" s="15" t="s">
+      <c r="I65" s="16" t="s">
         <v>421</v>
       </c>
-      <c r="H65" s="16" t="s">
-        <v>422</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>105</v>
-      </c>
       <c r="J65" s="5" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L65" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M65" s="5"/>
-      <c r="N65" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M65" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N65" s="5"/>
       <c r="O65" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P65" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q65" s="5"/>
-      <c r="R65" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q65" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R65" s="5"/>
       <c r="S65" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="66" spans="1:38" ht="28">
+        <v>25</v>
+      </c>
+      <c r="T65" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:39" ht="28">
       <c r="A66" s="17">
         <v>46085</v>
       </c>
@@ -6278,52 +6409,53 @@
         <v>46077</v>
       </c>
       <c r="C66" s="17"/>
-      <c r="D66" s="5" t="s">
-        <v>216</v>
-      </c>
+      <c r="D66" s="17"/>
       <c r="E66" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="G66" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="H66" s="15" t="s">
         <v>424</v>
       </c>
-      <c r="G66" s="15" t="s">
+      <c r="I66" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="H66" s="16" t="s">
+      <c r="J66" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="I66" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="K66" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L66" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M66" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N66" s="5"/>
       <c r="O66" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P66" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q66" s="5"/>
-      <c r="R66" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q66" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R66" s="5"/>
       <c r="S66" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="67" spans="1:38" ht="38">
+        <v>25</v>
+      </c>
+      <c r="T66" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:39" ht="38">
       <c r="A67" s="17">
         <v>46085</v>
       </c>
@@ -6331,167 +6463,174 @@
         <v>46077</v>
       </c>
       <c r="C67" s="17"/>
-      <c r="D67" s="5" t="s">
-        <v>216</v>
-      </c>
+      <c r="D67" s="17"/>
       <c r="E67" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="G67" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="H67" s="15" t="s">
         <v>429</v>
       </c>
-      <c r="G67" s="15" t="s">
+      <c r="I67" s="37" t="s">
         <v>430</v>
       </c>
-      <c r="H67" s="37" t="s">
+      <c r="J67" s="37" t="s">
         <v>431</v>
       </c>
-      <c r="I67" s="37" t="s">
+      <c r="K67" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L67" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="J67" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K67" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L67" s="5"/>
-      <c r="M67" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="N67" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="O67" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P67" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q67" s="5"/>
-      <c r="R67" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q67" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R67" s="5"/>
       <c r="S67" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="68" spans="1:38" ht="88">
+        <v>25</v>
+      </c>
+      <c r="T67" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:39" ht="88">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
-      <c r="D68" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="E68" s="9" t="s">
+      <c r="D68" s="5"/>
+      <c r="E68" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="G68" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="F68" s="9" t="s">
+      <c r="H68" s="60" t="s">
         <v>435</v>
       </c>
-      <c r="G68" s="62" t="s">
+      <c r="I68" s="52" t="s">
         <v>436</v>
       </c>
-      <c r="H68" s="55" t="s">
+      <c r="J68" s="52"/>
+      <c r="K68" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L68" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="M68" s="9"/>
+      <c r="N68" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="I68" s="55"/>
-      <c r="J68" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="K68" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L68" s="9"/>
-      <c r="M68" s="9" t="s">
+      <c r="O68" s="9"/>
+      <c r="P68" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="N68" s="9"/>
-      <c r="O68" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="P68" s="9"/>
       <c r="Q68" s="9"/>
       <c r="R68" s="9"/>
       <c r="S68" s="9"/>
-      <c r="T68" s="63"/>
-      <c r="U68" s="63"/>
-      <c r="V68" s="63"/>
-      <c r="W68" s="63"/>
-      <c r="X68" s="63"/>
-      <c r="Y68" s="63"/>
-      <c r="Z68" s="63"/>
-      <c r="AA68" s="63"/>
-      <c r="AB68" s="63"/>
-      <c r="AC68" s="63"/>
-      <c r="AD68" s="63"/>
-      <c r="AE68" s="63"/>
-    </row>
-    <row r="69" spans="1:38" ht="25.5">
-      <c r="A69" s="64">
+      <c r="T68" s="9"/>
+      <c r="U68" s="61"/>
+      <c r="V68" s="61"/>
+      <c r="W68" s="61"/>
+      <c r="X68" s="61"/>
+      <c r="Y68" s="61"/>
+      <c r="Z68" s="61"/>
+      <c r="AA68" s="61"/>
+      <c r="AB68" s="61"/>
+      <c r="AC68" s="61"/>
+      <c r="AD68" s="61"/>
+      <c r="AE68" s="61"/>
+      <c r="AF68" s="61"/>
+    </row>
+    <row r="69" spans="1:39" ht="56">
+      <c r="A69" s="62">
         <v>46084</v>
       </c>
-      <c r="B69" s="64">
+      <c r="B69" s="62">
         <v>46077</v>
       </c>
-      <c r="C69" s="64"/>
-      <c r="D69" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E69" s="9" t="s">
+      <c r="C69" s="62"/>
+      <c r="D69" s="62"/>
+      <c r="E69" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="G69" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="H69" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="G69" s="7" t="s">
+      <c r="I69" s="37" t="s">
         <v>442</v>
       </c>
-      <c r="H69" s="94" t="s">
+      <c r="J69" s="37" t="s">
         <v>443</v>
       </c>
-      <c r="I69" s="93"/>
-      <c r="J69" s="5"/>
-      <c r="K69" s="5"/>
+      <c r="K69" s="5" t="s">
+        <v>444</v>
+      </c>
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
-      <c r="O69" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="P69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5" t="s">
+        <v>445</v>
+      </c>
       <c r="Q69" s="5"/>
       <c r="R69" s="5"/>
       <c r="S69" s="5"/>
-    </row>
-    <row r="70" spans="1:38" ht="38">
-      <c r="A70" s="64">
+      <c r="T69" s="5"/>
+    </row>
+    <row r="70" spans="1:39" ht="38">
+      <c r="A70" s="62">
         <f>B70+5</f>
         <v>46081</v>
       </c>
-      <c r="B70" s="64">
+      <c r="B70" s="62">
         <v>46076</v>
       </c>
-      <c r="C70" s="64"/>
-      <c r="D70" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E70" s="9" t="s">
-        <v>445</v>
+      <c r="C70" s="62"/>
+      <c r="D70" s="62"/>
+      <c r="E70" s="5" t="s">
+        <v>134</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="G70" s="62" t="s">
+      <c r="G70" s="9" t="s">
         <v>447</v>
       </c>
-      <c r="H70" s="66" t="s">
+      <c r="H70" s="60" t="s">
         <v>448</v>
       </c>
-      <c r="I70" s="9" t="s">
+      <c r="I70" s="63" t="s">
         <v>449</v>
       </c>
-      <c r="J70" s="5"/>
+      <c r="J70" s="9" t="s">
+        <v>450</v>
+      </c>
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
       <c r="M70" s="5"/>
@@ -6501,190 +6640,194 @@
       <c r="Q70" s="5"/>
       <c r="R70" s="5"/>
       <c r="S70" s="5"/>
-    </row>
-    <row r="71" spans="1:38" ht="50.5">
-      <c r="A71" s="67">
+      <c r="T70" s="5"/>
+    </row>
+    <row r="71" spans="1:39" ht="50.5">
+      <c r="A71" s="64">
         <v>46085</v>
       </c>
-      <c r="B71" s="57"/>
-      <c r="C71" s="57"/>
-      <c r="D71" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E71" s="68" t="s">
-        <v>450</v>
-      </c>
-      <c r="F71" s="68" t="s">
+      <c r="B71" s="55"/>
+      <c r="C71" s="55"/>
+      <c r="D71" s="55"/>
+      <c r="E71" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" s="65" t="s">
         <v>451</v>
       </c>
-      <c r="G71" s="69" t="s">
+      <c r="G71" s="65" t="s">
         <v>452</v>
       </c>
-      <c r="H71" s="70" t="s">
+      <c r="H71" s="66" t="s">
         <v>453</v>
       </c>
-      <c r="I71" s="57" t="s">
+      <c r="I71" s="67" t="s">
         <v>454</v>
       </c>
-      <c r="J71" s="57" t="s">
+      <c r="J71" s="55" t="s">
         <v>455</v>
       </c>
-      <c r="K71" s="57"/>
-      <c r="L71" s="68" t="s">
+      <c r="K71" s="55" t="s">
         <v>456</v>
       </c>
-      <c r="M71" s="57"/>
-      <c r="N71" s="57"/>
-      <c r="O71" s="57"/>
-      <c r="P71" s="57"/>
-      <c r="Q71" s="57"/>
-      <c r="R71" s="57"/>
-      <c r="S71" s="57"/>
-      <c r="T71" s="61"/>
-      <c r="U71" s="61"/>
-      <c r="V71" s="61"/>
-      <c r="W71" s="61"/>
-      <c r="X71" s="61"/>
-      <c r="Y71" s="61"/>
-      <c r="Z71" s="61"/>
-      <c r="AA71" s="61"/>
-      <c r="AB71" s="61"/>
-      <c r="AC71" s="61"/>
-      <c r="AD71" s="61"/>
-      <c r="AE71" s="61"/>
-      <c r="AF71" s="61"/>
-      <c r="AG71" s="61"/>
-      <c r="AH71" s="61"/>
-      <c r="AI71" s="61"/>
-      <c r="AJ71" s="61"/>
-      <c r="AK71" s="61"/>
-      <c r="AL71" s="61"/>
-    </row>
-    <row r="72" spans="1:38" ht="50.5">
-      <c r="A72" s="64">
+      <c r="L71" s="55"/>
+      <c r="M71" s="65" t="s">
+        <v>457</v>
+      </c>
+      <c r="N71" s="55"/>
+      <c r="O71" s="55"/>
+      <c r="P71" s="55"/>
+      <c r="Q71" s="55"/>
+      <c r="R71" s="55"/>
+      <c r="S71" s="55"/>
+      <c r="T71" s="55"/>
+      <c r="U71" s="59"/>
+      <c r="V71" s="59"/>
+      <c r="W71" s="59"/>
+      <c r="X71" s="59"/>
+      <c r="Y71" s="59"/>
+      <c r="Z71" s="59"/>
+      <c r="AA71" s="59"/>
+      <c r="AB71" s="59"/>
+      <c r="AC71" s="59"/>
+      <c r="AD71" s="59"/>
+      <c r="AE71" s="59"/>
+      <c r="AF71" s="59"/>
+      <c r="AG71" s="59"/>
+      <c r="AH71" s="59"/>
+      <c r="AI71" s="59"/>
+      <c r="AJ71" s="59"/>
+      <c r="AK71" s="59"/>
+      <c r="AL71" s="59"/>
+      <c r="AM71" s="59"/>
+    </row>
+    <row r="72" spans="1:39" ht="50.5">
+      <c r="A72" s="62">
         <f>B72+5</f>
         <v>46076</v>
       </c>
-      <c r="B72" s="64">
+      <c r="B72" s="62">
         <v>46071</v>
       </c>
-      <c r="C72" s="64"/>
-      <c r="D72" s="5" t="s">
-        <v>136</v>
-      </c>
+      <c r="C72" s="62"/>
+      <c r="D72" s="62"/>
       <c r="E72" s="5" t="s">
-        <v>457</v>
+        <v>134</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="G72" s="15" t="s">
+      <c r="G72" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="H72" s="16" t="s">
+      <c r="H72" s="15" t="s">
         <v>460</v>
       </c>
-      <c r="I72" s="28" t="s">
+      <c r="I72" s="16" t="s">
         <v>461</v>
       </c>
-      <c r="J72" s="5" t="s">
+      <c r="J72" s="28" t="s">
         <v>462</v>
       </c>
-      <c r="K72" s="5"/>
-      <c r="L72" s="25"/>
-      <c r="M72" s="71">
+      <c r="K72" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="L72" s="5"/>
+      <c r="M72" s="25"/>
+      <c r="N72" s="68">
         <v>46071.666666666664</v>
       </c>
-      <c r="N72" s="5"/>
       <c r="O72" s="5"/>
       <c r="P72" s="5"/>
       <c r="Q72" s="5"/>
       <c r="R72" s="5"/>
       <c r="S72" s="5"/>
-    </row>
-    <row r="73" spans="1:38" ht="70">
+      <c r="T72" s="5"/>
+    </row>
+    <row r="73" spans="1:39" ht="70">
       <c r="A73" s="5"/>
-      <c r="B73" s="72">
+      <c r="B73" s="69">
         <v>46077</v>
       </c>
-      <c r="C73" s="72"/>
-      <c r="D73" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>463</v>
+      <c r="C73" s="69"/>
+      <c r="D73" s="69"/>
+      <c r="E73" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="G73" s="73" t="s">
+      <c r="G73" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="H73" s="55" t="s">
+      <c r="H73" s="70" t="s">
         <v>466</v>
       </c>
-      <c r="I73" s="9" t="s">
+      <c r="I73" s="52" t="s">
         <v>467</v>
       </c>
       <c r="J73" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="K73" s="57" t="s">
+      <c r="K73" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="L73" s="9" t="s">
+      <c r="L73" s="55" t="s">
         <v>470</v>
       </c>
-      <c r="M73" s="9"/>
+      <c r="M73" s="9" t="s">
+        <v>471</v>
+      </c>
       <c r="N73" s="9"/>
       <c r="O73" s="9"/>
       <c r="P73" s="9"/>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
       <c r="S73" s="9"/>
-      <c r="T73" s="63"/>
-      <c r="U73" s="63"/>
-      <c r="V73" s="63"/>
-      <c r="W73" s="63"/>
-      <c r="X73" s="63"/>
-      <c r="Y73" s="63"/>
-      <c r="Z73" s="63"/>
-      <c r="AA73" s="63"/>
-      <c r="AB73" s="63"/>
-      <c r="AC73" s="63"/>
-      <c r="AD73" s="63"/>
-    </row>
-    <row r="74" spans="1:38" ht="38">
-      <c r="A74" s="64">
+      <c r="T73" s="9"/>
+      <c r="U73" s="61"/>
+      <c r="V73" s="61"/>
+      <c r="W73" s="61"/>
+      <c r="X73" s="61"/>
+      <c r="Y73" s="61"/>
+      <c r="Z73" s="61"/>
+      <c r="AA73" s="61"/>
+      <c r="AB73" s="61"/>
+      <c r="AC73" s="61"/>
+      <c r="AD73" s="61"/>
+      <c r="AE73" s="61"/>
+    </row>
+    <row r="74" spans="1:39" ht="38">
+      <c r="A74" s="62">
         <f t="shared" ref="A74:A75" si="0">B74+5</f>
         <v>46081</v>
       </c>
-      <c r="B74" s="64">
+      <c r="B74" s="62">
         <v>46076</v>
       </c>
-      <c r="C74" s="64"/>
-      <c r="D74" s="28" t="s">
-        <v>216</v>
-      </c>
+      <c r="C74" s="62"/>
+      <c r="D74" s="62"/>
       <c r="E74" s="28" t="s">
-        <v>471</v>
+        <v>214</v>
       </c>
       <c r="F74" s="28" t="s">
         <v>472</v>
       </c>
-      <c r="G74" s="74" t="s">
+      <c r="G74" s="28" t="s">
         <v>473</v>
       </c>
-      <c r="H74" s="16" t="s">
+      <c r="H74" s="71" t="s">
         <v>474</v>
       </c>
-      <c r="I74" s="28" t="s">
+      <c r="I74" s="16" t="s">
         <v>475</v>
       </c>
       <c r="J74" s="28" t="s">
         <v>476</v>
       </c>
-      <c r="K74" s="28"/>
+      <c r="K74" s="28" t="s">
+        <v>477</v>
+      </c>
       <c r="L74" s="28"/>
       <c r="M74" s="28"/>
       <c r="N74" s="28"/>
@@ -6693,38 +6836,39 @@
       <c r="Q74" s="28"/>
       <c r="R74" s="28"/>
       <c r="S74" s="28"/>
-    </row>
-    <row r="75" spans="1:38" ht="50.5">
-      <c r="A75" s="64">
+      <c r="T74" s="28"/>
+    </row>
+    <row r="75" spans="1:39" ht="50.5">
+      <c r="A75" s="62">
         <f t="shared" si="0"/>
         <v>46081</v>
       </c>
-      <c r="B75" s="64">
+      <c r="B75" s="62">
         <v>46076</v>
       </c>
-      <c r="C75" s="64"/>
-      <c r="D75" s="28" t="s">
-        <v>216</v>
-      </c>
+      <c r="C75" s="62"/>
+      <c r="D75" s="62"/>
       <c r="E75" s="28" t="s">
-        <v>477</v>
+        <v>214</v>
       </c>
       <c r="F75" s="28" t="s">
         <v>478</v>
       </c>
-      <c r="G75" s="75" t="s">
+      <c r="G75" s="28" t="s">
         <v>479</v>
       </c>
-      <c r="H75" s="37" t="s">
+      <c r="H75" s="72" t="s">
         <v>480</v>
       </c>
       <c r="I75" s="37" t="s">
         <v>481</v>
       </c>
-      <c r="J75" s="28" t="s">
+      <c r="J75" s="37" t="s">
         <v>482</v>
       </c>
-      <c r="K75" s="28"/>
+      <c r="K75" s="28" t="s">
+        <v>483</v>
+      </c>
       <c r="L75" s="28"/>
       <c r="M75" s="28"/>
       <c r="N75" s="28"/>
@@ -6733,34 +6877,35 @@
       <c r="Q75" s="28"/>
       <c r="R75" s="28"/>
       <c r="S75" s="28"/>
-    </row>
-    <row r="76" spans="1:38" ht="112.5">
+      <c r="T75" s="28"/>
+    </row>
+    <row r="76" spans="1:39" ht="112.5">
       <c r="A76" s="17">
         <v>46087</v>
       </c>
-      <c r="B76" s="64">
+      <c r="B76" s="62">
         <v>46079</v>
       </c>
-      <c r="C76" s="64"/>
-      <c r="D76" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="E76" s="76" t="s">
-        <v>483</v>
-      </c>
-      <c r="F76" s="76" t="s">
+      <c r="C76" s="62"/>
+      <c r="D76" s="62"/>
+      <c r="E76" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F76" s="73" t="s">
         <v>484</v>
       </c>
-      <c r="G76" s="77" t="s">
+      <c r="G76" s="73" t="s">
         <v>485</v>
       </c>
-      <c r="H76" s="76" t="s">
+      <c r="H76" s="74" t="s">
         <v>486</v>
       </c>
-      <c r="I76" s="78" t="s">
+      <c r="I76" s="73" t="s">
         <v>487</v>
       </c>
-      <c r="J76" s="28"/>
+      <c r="J76" s="75" t="s">
+        <v>488</v>
+      </c>
       <c r="K76" s="28"/>
       <c r="L76" s="28"/>
       <c r="M76" s="28"/>
@@ -6770,442 +6915,709 @@
       <c r="Q76" s="28"/>
       <c r="R76" s="28"/>
       <c r="S76" s="28"/>
-    </row>
-    <row r="77" spans="1:38" ht="14">
-      <c r="A77" s="52"/>
-      <c r="B77" s="52"/>
-      <c r="C77" s="52"/>
-      <c r="D77" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="E77" s="52" t="s">
-        <v>488</v>
-      </c>
-      <c r="F77" s="52" t="s">
+      <c r="T76" s="28"/>
+    </row>
+    <row r="77" spans="1:39" ht="42">
+      <c r="A77" s="28"/>
+      <c r="B77" s="28"/>
+      <c r="C77" s="28"/>
+      <c r="D77" s="28"/>
+      <c r="E77" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="F77" s="28" t="s">
         <v>489</v>
       </c>
-      <c r="G77" s="79" t="s">
+      <c r="G77" s="28" t="s">
         <v>490</v>
       </c>
-      <c r="H77" s="65" t="s">
+      <c r="H77" s="72" t="s">
         <v>491</v>
       </c>
-      <c r="I77" s="80" t="s">
+      <c r="I77" s="37" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="78" spans="1:38" ht="14">
-      <c r="A78" s="64">
+      <c r="J77" s="76" t="s">
+        <v>493</v>
+      </c>
+      <c r="K77" s="28"/>
+      <c r="L77" s="28"/>
+      <c r="M77" s="28"/>
+      <c r="N77" s="28"/>
+      <c r="O77" s="28"/>
+      <c r="P77" s="28"/>
+      <c r="Q77" s="28"/>
+      <c r="R77" s="28"/>
+      <c r="S77" s="28"/>
+      <c r="T77" s="28"/>
+    </row>
+    <row r="78" spans="1:39" ht="50.5">
+      <c r="A78" s="62">
         <v>46086</v>
       </c>
-      <c r="B78" s="64">
+      <c r="B78" s="62">
         <v>46077</v>
       </c>
-      <c r="C78" s="64"/>
-      <c r="D78" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="E78" s="52" t="s">
-        <v>493</v>
-      </c>
-      <c r="F78" s="52" t="s">
+      <c r="C78" s="62"/>
+      <c r="D78" s="62"/>
+      <c r="E78" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78" s="28" t="s">
         <v>494</v>
       </c>
-      <c r="G78" s="79" t="s">
+      <c r="G78" s="28" t="s">
         <v>495</v>
       </c>
-      <c r="H78" s="65" t="s">
+      <c r="H78" s="72" t="s">
         <v>496</v>
       </c>
-      <c r="I78" s="52" t="s">
+      <c r="I78" s="37" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="79" spans="1:38" ht="14">
-      <c r="A79" s="64">
+      <c r="J78" s="28" t="s">
+        <v>498</v>
+      </c>
+      <c r="K78" s="28"/>
+      <c r="L78" s="28"/>
+      <c r="M78" s="28"/>
+      <c r="N78" s="28"/>
+      <c r="O78" s="28"/>
+      <c r="P78" s="28"/>
+      <c r="Q78" s="28"/>
+      <c r="R78" s="28"/>
+      <c r="S78" s="28"/>
+      <c r="T78" s="28"/>
+    </row>
+    <row r="79" spans="1:39" ht="50.5">
+      <c r="A79" s="62">
         <v>46086</v>
       </c>
-      <c r="B79" s="64">
+      <c r="B79" s="62">
         <v>46078</v>
       </c>
-      <c r="C79" s="64"/>
-      <c r="D79" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="E79" s="52" t="s">
-        <v>498</v>
-      </c>
-      <c r="F79" s="52" t="s">
+      <c r="C79" s="62"/>
+      <c r="D79" s="62"/>
+      <c r="E79" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F79" s="28" t="s">
         <v>499</v>
       </c>
-      <c r="G79" s="79" t="s">
+      <c r="G79" s="28" t="s">
         <v>500</v>
       </c>
-      <c r="H79" s="65" t="s">
+      <c r="H79" s="72" t="s">
         <v>501</v>
       </c>
-      <c r="I79" s="52" t="s">
+      <c r="I79" s="37" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="80" spans="1:38" ht="14">
-      <c r="A80" s="64">
+      <c r="J79" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="K79" s="28"/>
+      <c r="L79" s="28"/>
+      <c r="M79" s="28"/>
+      <c r="N79" s="28"/>
+      <c r="O79" s="28"/>
+      <c r="P79" s="28"/>
+      <c r="Q79" s="28"/>
+      <c r="R79" s="28"/>
+      <c r="S79" s="28"/>
+      <c r="T79" s="28"/>
+    </row>
+    <row r="80" spans="1:39" ht="28">
+      <c r="A80" s="62">
         <v>46087</v>
       </c>
-      <c r="B80" s="64">
+      <c r="B80" s="62">
         <v>46079</v>
       </c>
-      <c r="C80" s="64"/>
-      <c r="D80" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="E80" s="52" t="s">
-        <v>503</v>
-      </c>
-      <c r="F80" s="52" t="s">
+      <c r="C80" s="62"/>
+      <c r="D80" s="62"/>
+      <c r="E80" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F80" s="28" t="s">
         <v>504</v>
       </c>
-      <c r="G80" s="52" t="s">
-        <v>503</v>
-      </c>
-      <c r="H80" s="65" t="s">
+      <c r="G80" s="28" t="s">
         <v>505</v>
       </c>
-      <c r="I80" s="65"/>
-      <c r="J80" s="52" t="s">
+      <c r="H80" s="28" t="s">
+        <v>504</v>
+      </c>
+      <c r="I80" s="37" t="s">
         <v>506</v>
       </c>
-      <c r="M80" s="61" t="s">
+      <c r="J80" s="37"/>
+      <c r="K80" s="28" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" ht="14">
-      <c r="A81" s="64">
+      <c r="L80" s="28"/>
+      <c r="M80" s="28"/>
+      <c r="N80" s="55" t="s">
+        <v>508</v>
+      </c>
+      <c r="O80" s="28"/>
+      <c r="P80" s="28"/>
+      <c r="Q80" s="28"/>
+      <c r="R80" s="28"/>
+      <c r="S80" s="28"/>
+      <c r="T80" s="28"/>
+    </row>
+    <row r="81" spans="1:20" ht="76.5">
+      <c r="A81" s="62">
         <v>46087</v>
       </c>
-      <c r="B81" s="64">
+      <c r="B81" s="62">
         <v>46080</v>
       </c>
-      <c r="C81" s="64"/>
-      <c r="D81" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="E81" s="52" t="s">
-        <v>508</v>
-      </c>
-      <c r="F81" s="52" t="s">
+      <c r="C81" s="62"/>
+      <c r="D81" s="62"/>
+      <c r="E81" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F81" s="28" t="s">
         <v>509</v>
       </c>
-      <c r="G81" s="79" t="s">
+      <c r="G81" s="28" t="s">
         <v>510</v>
       </c>
-      <c r="H81" s="81" t="s">
+      <c r="H81" s="72" t="s">
         <v>511</v>
       </c>
-      <c r="I81" s="63" t="s">
+      <c r="I81" s="45" t="s">
         <v>512</v>
       </c>
-      <c r="M81" s="82" t="s">
+      <c r="J81" s="73" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="82" spans="1:13" ht="14">
-      <c r="A82" s="63"/>
+      <c r="K81" s="28"/>
+      <c r="L81" s="28"/>
+      <c r="M81" s="28"/>
+      <c r="N81" s="77" t="s">
+        <v>514</v>
+      </c>
+      <c r="O81" s="28"/>
+      <c r="P81" s="28"/>
+      <c r="Q81" s="28"/>
+      <c r="R81" s="28"/>
+      <c r="S81" s="28"/>
+      <c r="T81" s="28"/>
+    </row>
+    <row r="82" spans="1:20" ht="38">
+      <c r="A82" s="73"/>
       <c r="B82" s="17">
         <v>46080</v>
       </c>
       <c r="C82" s="17"/>
-      <c r="D82" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="E82" s="63" t="s">
-        <v>514</v>
-      </c>
-      <c r="F82" s="63" t="s">
+      <c r="D82" s="17"/>
+      <c r="E82" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" s="73" t="s">
         <v>515</v>
       </c>
-      <c r="G82" s="77" t="s">
+      <c r="G82" s="73" t="s">
         <v>516</v>
       </c>
-      <c r="H82" s="56" t="s">
+      <c r="H82" s="74" t="s">
         <v>517</v>
       </c>
-      <c r="I82" s="83"/>
-      <c r="L82" s="84" t="s">
+      <c r="I82" s="52" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="83" spans="1:13" ht="14">
-      <c r="A83" s="63"/>
+      <c r="J82" s="78"/>
+      <c r="K82" s="28"/>
+      <c r="L82" s="28"/>
+      <c r="M82" s="79" t="s">
+        <v>519</v>
+      </c>
+      <c r="N82" s="28"/>
+      <c r="O82" s="28"/>
+      <c r="P82" s="28"/>
+      <c r="Q82" s="28"/>
+      <c r="R82" s="28"/>
+      <c r="S82" s="28"/>
+      <c r="T82" s="28"/>
+    </row>
+    <row r="83" spans="1:20" ht="88">
+      <c r="A83" s="62">
+        <v>46086</v>
+      </c>
       <c r="B83" s="17">
         <v>46080</v>
       </c>
       <c r="C83" s="17"/>
-      <c r="D83" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="E83" s="76" t="s">
-        <v>519</v>
-      </c>
-      <c r="F83" s="63" t="s">
+      <c r="D83" s="17"/>
+      <c r="E83" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83" s="73" t="s">
         <v>520</v>
       </c>
-      <c r="G83" s="77" t="s">
+      <c r="G83" s="73" t="s">
         <v>521</v>
       </c>
-      <c r="H83" s="85" t="s">
+      <c r="H83" s="74" t="s">
         <v>522</v>
       </c>
-      <c r="I83" s="63"/>
-      <c r="M83" s="86" t="s">
+      <c r="I83" s="80" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" ht="26">
-      <c r="D84" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="E84" s="63" t="s">
+      <c r="J83" s="73"/>
+      <c r="K83" s="28"/>
+      <c r="L83" s="28" t="s">
         <v>524</v>
       </c>
-      <c r="F84" s="63" t="s">
+      <c r="M83" s="28"/>
+      <c r="N83" s="65" t="s">
         <v>525</v>
       </c>
-      <c r="G84" s="77" t="s">
+      <c r="O83" s="28"/>
+      <c r="P83" s="81" t="s">
         <v>526</v>
       </c>
-      <c r="H84" s="76" t="s">
+      <c r="Q83" s="28"/>
+      <c r="R83" s="28"/>
+      <c r="S83" s="28"/>
+      <c r="T83" s="28"/>
+    </row>
+    <row r="84" spans="1:20" ht="63.5">
+      <c r="A84" s="62">
+        <v>46086</v>
+      </c>
+      <c r="B84" s="28"/>
+      <c r="C84" s="28"/>
+      <c r="D84" s="28"/>
+      <c r="E84" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="F84" s="73" t="s">
         <v>527</v>
       </c>
-      <c r="I84" s="87" t="s">
+      <c r="G84" s="73" t="s">
         <v>528</v>
       </c>
-      <c r="J84" s="52" t="s">
+      <c r="H84" s="74" t="s">
         <v>529</v>
       </c>
-      <c r="M84" s="88" t="s">
+      <c r="I84" s="73" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="85" spans="1:13" ht="16">
-      <c r="D85" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="E85" s="63" t="s">
+      <c r="J84" s="82" t="s">
         <v>531</v>
       </c>
-      <c r="F85" s="63" t="s">
+      <c r="K84" s="28" t="s">
         <v>532</v>
       </c>
-      <c r="G85" s="77" t="s">
+      <c r="L84" s="28" t="s">
+        <v>524</v>
+      </c>
+      <c r="M84" s="28"/>
+      <c r="N84" s="83" t="s">
         <v>533</v>
       </c>
-      <c r="H85" s="56" t="s">
+      <c r="O84" s="28"/>
+      <c r="P84" s="28"/>
+      <c r="Q84" s="28"/>
+      <c r="R84" s="28"/>
+      <c r="S84" s="28"/>
+      <c r="T84" s="28"/>
+    </row>
+    <row r="85" spans="1:20" ht="64">
+      <c r="A85" s="28"/>
+      <c r="B85" s="28"/>
+      <c r="C85" s="28"/>
+      <c r="D85" s="28"/>
+      <c r="E85" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="F85" s="73" t="s">
         <v>534</v>
       </c>
-      <c r="I85" s="56" t="s">
+      <c r="G85" s="73" t="s">
         <v>535</v>
       </c>
-      <c r="J85" s="89" t="s">
+      <c r="H85" s="74" t="s">
         <v>536</v>
       </c>
-      <c r="M85" s="90" t="s">
+      <c r="I85" s="52" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" ht="14">
-      <c r="D86" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="E86" s="63" t="s">
+      <c r="J85" s="52" t="s">
         <v>538</v>
       </c>
-      <c r="F86" s="63" t="s">
+      <c r="K85" s="25" t="s">
         <v>539</v>
       </c>
-      <c r="G86" s="77" t="s">
+      <c r="L85" s="28"/>
+      <c r="M85" s="28"/>
+      <c r="N85" s="84" t="s">
         <v>540</v>
       </c>
-      <c r="H86" s="85" t="s">
+      <c r="O85" s="28"/>
+      <c r="P85" s="28"/>
+      <c r="Q85" s="28"/>
+      <c r="R85" s="28"/>
+      <c r="S85" s="28"/>
+      <c r="T85" s="28"/>
+    </row>
+    <row r="86" spans="1:20" ht="50">
+      <c r="A86" s="28"/>
+      <c r="B86" s="28"/>
+      <c r="C86" s="28"/>
+      <c r="D86" s="28"/>
+      <c r="E86" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F86" s="73" t="s">
         <v>541</v>
       </c>
-      <c r="I86" s="63" t="s">
+      <c r="G86" s="73" t="s">
         <v>542</v>
       </c>
-      <c r="J86" s="63" t="s">
+      <c r="H86" s="74" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" ht="14">
-      <c r="D87" s="52" t="s">
-        <v>333</v>
-      </c>
-      <c r="E87" s="63" t="s">
+      <c r="I86" s="80" t="s">
         <v>544</v>
       </c>
-      <c r="F87" s="63" t="s">
+      <c r="J86" s="73" t="s">
         <v>545</v>
       </c>
-      <c r="G87" s="77" t="s">
+      <c r="K86" s="73" t="s">
         <v>546</v>
       </c>
-      <c r="H87" s="56" t="s">
+      <c r="L86" s="28"/>
+      <c r="M86" s="28"/>
+      <c r="N86" s="28"/>
+      <c r="O86" s="28"/>
+      <c r="P86" s="28"/>
+      <c r="Q86" s="28"/>
+      <c r="R86" s="28"/>
+      <c r="S86" s="28"/>
+      <c r="T86" s="28"/>
+    </row>
+    <row r="87" spans="1:20" ht="67.5">
+      <c r="A87" s="28"/>
+      <c r="B87" s="28"/>
+      <c r="C87" s="28"/>
+      <c r="D87" s="28"/>
+      <c r="E87" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="F87" s="73" t="s">
         <v>547</v>
       </c>
-      <c r="I87" s="91" t="s">
+      <c r="G87" s="73" t="s">
         <v>548</v>
       </c>
-      <c r="J87" s="63" t="s">
+      <c r="H87" s="74" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="88" spans="1:13" ht="14">
-      <c r="D88" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="E88" s="63" t="s">
+      <c r="I87" s="52" t="s">
         <v>550</v>
       </c>
-      <c r="F88" s="63" t="s">
+      <c r="J87" s="85" t="s">
         <v>551</v>
       </c>
-      <c r="G88" s="77" t="s">
+      <c r="K87" s="73" t="s">
         <v>552</v>
       </c>
-      <c r="H88" s="85" t="s">
+      <c r="L87" s="28"/>
+      <c r="M87" s="28"/>
+      <c r="N87" s="28"/>
+      <c r="O87" s="28"/>
+      <c r="P87" s="28"/>
+      <c r="Q87" s="28"/>
+      <c r="R87" s="28"/>
+      <c r="S87" s="28"/>
+      <c r="T87" s="28"/>
+    </row>
+    <row r="88" spans="1:20" ht="42">
+      <c r="A88" s="28"/>
+      <c r="B88" s="28"/>
+      <c r="C88" s="28"/>
+      <c r="D88" s="28"/>
+      <c r="E88" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="F88" s="73" t="s">
         <v>553</v>
       </c>
-      <c r="I88" s="52" t="s">
+      <c r="G88" s="73" t="s">
         <v>554</v>
       </c>
-      <c r="J88" s="86" t="s">
+      <c r="H88" s="74" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="89" spans="1:13" ht="14">
-      <c r="D89" s="52" t="s">
-        <v>333</v>
-      </c>
-      <c r="E89" s="63" t="s">
+      <c r="I88" s="80" t="s">
         <v>556</v>
       </c>
-      <c r="F89" s="63" t="s">
+      <c r="J88" s="28" t="s">
         <v>557</v>
       </c>
-      <c r="G89" s="77" t="s">
+      <c r="K88" s="65" t="s">
         <v>558</v>
       </c>
-      <c r="H89" s="56" t="s">
+      <c r="L88" s="28"/>
+      <c r="M88" s="28"/>
+      <c r="N88" s="28"/>
+      <c r="O88" s="28"/>
+      <c r="P88" s="28"/>
+      <c r="Q88" s="28"/>
+      <c r="R88" s="28"/>
+      <c r="S88" s="28"/>
+      <c r="T88" s="28"/>
+    </row>
+    <row r="89" spans="1:20" ht="50">
+      <c r="A89" s="28"/>
+      <c r="B89" s="28"/>
+      <c r="C89" s="28"/>
+      <c r="D89" s="28"/>
+      <c r="E89" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="F89" s="73" t="s">
         <v>559</v>
       </c>
-      <c r="I89" s="89" t="s">
+      <c r="G89" s="73" t="s">
         <v>560</v>
       </c>
-      <c r="J89" s="89" t="s">
+      <c r="H89" s="74" t="s">
         <v>561</v>
       </c>
+      <c r="I89" s="52" t="s">
+        <v>562</v>
+      </c>
+      <c r="J89" s="25" t="s">
+        <v>563</v>
+      </c>
+      <c r="K89" s="25" t="s">
+        <v>564</v>
+      </c>
+      <c r="L89" s="28"/>
+      <c r="M89" s="28"/>
+      <c r="N89" s="28"/>
+      <c r="O89" s="28"/>
+      <c r="P89" s="28"/>
+      <c r="Q89" s="28"/>
+      <c r="R89" s="28"/>
+      <c r="S89" s="28"/>
+      <c r="T89" s="28"/>
+    </row>
+    <row r="90" spans="1:20" ht="50">
+      <c r="A90" s="28"/>
+      <c r="B90" s="28"/>
+      <c r="C90" s="28"/>
+      <c r="D90" s="28"/>
+      <c r="E90" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F90" s="28" t="s">
+        <v>565</v>
+      </c>
+      <c r="G90" s="28" t="s">
+        <v>566</v>
+      </c>
+      <c r="H90" s="28"/>
+      <c r="I90" s="37" t="s">
+        <v>567</v>
+      </c>
+      <c r="J90" s="37"/>
+      <c r="K90" s="28"/>
+      <c r="L90" s="28"/>
+      <c r="M90" s="28"/>
+      <c r="N90" s="55" t="s">
+        <v>580</v>
+      </c>
+      <c r="O90" s="28"/>
+      <c r="P90" s="28"/>
+      <c r="Q90" s="28"/>
+      <c r="R90" s="28"/>
+      <c r="S90" s="28"/>
+      <c r="T90" s="28"/>
+    </row>
+    <row r="91" spans="1:20" ht="50">
+      <c r="A91" s="28"/>
+      <c r="B91" s="28"/>
+      <c r="C91" s="28"/>
+      <c r="D91" s="28"/>
+      <c r="E91" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F91" s="28"/>
+      <c r="G91" s="28" t="s">
+        <v>568</v>
+      </c>
+      <c r="H91" s="28"/>
+      <c r="I91" s="37" t="s">
+        <v>569</v>
+      </c>
+      <c r="J91" s="37"/>
+      <c r="K91" s="28"/>
+      <c r="L91" s="28"/>
+      <c r="M91" s="28"/>
+      <c r="N91" s="28"/>
+      <c r="O91" s="28"/>
+      <c r="P91" s="28"/>
+      <c r="Q91" s="28"/>
+      <c r="R91" s="28"/>
+      <c r="S91" s="28"/>
+      <c r="T91" s="28"/>
+    </row>
+    <row r="92" spans="1:20" ht="46.5">
+      <c r="A92" s="28"/>
+      <c r="B92" s="28"/>
+      <c r="C92" s="28"/>
+      <c r="D92" s="28"/>
+      <c r="E92" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F92" s="28" t="s">
+        <v>570</v>
+      </c>
+      <c r="G92" s="86" t="s">
+        <v>571</v>
+      </c>
+      <c r="H92" s="48" t="s">
+        <v>572</v>
+      </c>
+      <c r="I92" s="28" t="s">
+        <v>573</v>
+      </c>
+      <c r="J92" s="28" t="s">
+        <v>574</v>
+      </c>
+      <c r="K92" s="28" t="s">
+        <v>575</v>
+      </c>
+      <c r="L92" s="28"/>
+      <c r="M92" s="28"/>
+      <c r="N92" s="28"/>
+      <c r="O92" s="28"/>
+      <c r="P92" s="28"/>
+      <c r="Q92" s="28"/>
+      <c r="R92" s="28"/>
+      <c r="S92" s="28"/>
+      <c r="T92" s="28"/>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E1003" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="2">
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H69:I69"/>
+  <autoFilter ref="F1:F1003" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <mergeCells count="1">
+    <mergeCell ref="I37:J37"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="G3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="G5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="G6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="J6" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="G7" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="G8" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="G9" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="G10" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="G11" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="G12" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="G13" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="G14" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="G15" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="G16" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="G17" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="G18" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="G19" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="G20" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="G21" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="G22" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="G23" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="G24" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="G25" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="G26" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="G27" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="G28" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="G29" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="G31" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="G32" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="G33" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="G34" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="G35" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="H35" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="G36" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="G37" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="G38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="G39" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="G40" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="G41" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="G42" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="G43" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="G44" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="G45" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="G46" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="H46" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="G47" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="G48" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="G49" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="E50" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="G50" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="G51" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="H51" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="G52" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="G53" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="G54" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="G55" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="G56" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="G57" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="G58" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="G59" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="G60" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="G61" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="E62" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="G62" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="G63" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="G64" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="G65" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="G66" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="G67" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="G68" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="G69" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="G70" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="G71" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="G72" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="G73" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="G74" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="G75" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="G76" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="G77" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="G78" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="G79" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="G81" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="G82" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="G83" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="G84" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="G85" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="G86" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="G87" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="G88" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="G89" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="H3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="H4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="H5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="H6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="K6" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="H7" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="H8" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="H9" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="H10" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="H11" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="H12" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="H13" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="H14" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="H15" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="H16" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="H17" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="H18" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="H19" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="H20" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="H21" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="H22" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="H23" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="H24" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="H25" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="H26" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="H27" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="H28" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="H29" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="H31" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="H32" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="H33" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="H34" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="H35" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="I35" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="H36" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="H37" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="H38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="H39" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="H40" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="H41" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="H42" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="H43" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="H44" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="H45" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="H46" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="I46" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="H47" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="H48" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="H49" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="F50" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="H50" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="H51" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="I51" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="H52" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="H53" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="H54" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="H55" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="H56" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="H57" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="H58" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="H59" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="H60" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="H61" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="F62" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="H62" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="H63" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="H64" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="H65" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="H66" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="H67" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="H68" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="H69" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="H70" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="H71" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="H72" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="H73" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="H74" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="H75" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="H76" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="H77" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="H78" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="H79" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="H81" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="H82" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="H83" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="H84" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="H85" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="H86" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="H87" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="H88" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="H89" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="H92" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>